--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7800,6 +7800,111 @@
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131970205</v>
+      </c>
+      <c r="B74" t="n">
+        <v>56475</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Långfallsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>465360</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6790880</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131930995</v>
       </c>
       <c r="B2" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131933992</v>
       </c>
       <c r="B3" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131933662</v>
       </c>
       <c r="B4" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131929045</v>
       </c>
       <c r="B5" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131933929</v>
       </c>
       <c r="B6" t="n">
-        <v>97910</v>
+        <v>97912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,53 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131932655</v>
+        <v>131930461</v>
       </c>
       <c r="B7" t="n">
-        <v>57897</v>
+        <v>79269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465613</v>
+        <v>465359</v>
       </c>
       <c r="R7" t="n">
-        <v>6790943</v>
+        <v>6790942</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1262,48 +1257,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131930461</v>
+        <v>131932655</v>
       </c>
       <c r="B8" t="n">
-        <v>79267</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465359</v>
+        <v>465613</v>
       </c>
       <c r="R8" t="n">
-        <v>6790942</v>
+        <v>6790943</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131928067</v>
+        <v>131933121</v>
       </c>
       <c r="B9" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465342</v>
+        <v>465608</v>
       </c>
       <c r="R9" t="n">
-        <v>6790879</v>
+        <v>6790896</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131931121</v>
+        <v>131933933</v>
       </c>
       <c r="B10" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465451</v>
+        <v>465563</v>
       </c>
       <c r="R10" t="n">
-        <v>6790896</v>
+        <v>6790864</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1527,11 +1527,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131927769</v>
+        <v>131931121</v>
       </c>
       <c r="B11" t="n">
-        <v>57905</v>
+        <v>79269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,42 +1564,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465338</v>
+        <v>465451</v>
       </c>
       <c r="R11" t="n">
-        <v>6790853</v>
+        <v>6790896</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1634,6 +1624,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131934127</v>
+        <v>131929201</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>79269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,42 +1666,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465537</v>
+        <v>465380</v>
       </c>
       <c r="R12" t="n">
-        <v>6790847</v>
+        <v>6790900</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1762,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131933121</v>
+        <v>131928067</v>
       </c>
       <c r="B13" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,13 +1787,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465608</v>
+        <v>465342</v>
       </c>
       <c r="R13" t="n">
-        <v>6790896</v>
+        <v>6790879</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1859,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131929201</v>
+        <v>131934127</v>
       </c>
       <c r="B14" t="n">
-        <v>79267</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,37 +1860,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465380</v>
+        <v>465537</v>
       </c>
       <c r="R14" t="n">
-        <v>6790900</v>
+        <v>6790847</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1956,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131933933</v>
+        <v>131927769</v>
       </c>
       <c r="B15" t="n">
-        <v>79267</v>
+        <v>57907</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,34 +1962,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465563</v>
+        <v>465338</v>
       </c>
       <c r="R15" t="n">
-        <v>6790864</v>
+        <v>6790853</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131931931</v>
+        <v>131931225</v>
       </c>
       <c r="B16" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465523</v>
+        <v>465472</v>
       </c>
       <c r="R16" t="n">
-        <v>6790868</v>
+        <v>6790889</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131931225</v>
+        <v>131931931</v>
       </c>
       <c r="B17" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465472</v>
+        <v>465523</v>
       </c>
       <c r="R17" t="n">
-        <v>6790889</v>
+        <v>6790868</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131932719</v>
+        <v>131930082</v>
       </c>
       <c r="B18" t="n">
-        <v>57905</v>
+        <v>79269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,42 +2258,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465613</v>
+        <v>465351</v>
       </c>
       <c r="R18" t="n">
-        <v>6790943</v>
+        <v>6790929</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2349,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131930082</v>
+        <v>131932725</v>
       </c>
       <c r="B19" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2384,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465351</v>
+        <v>465613</v>
       </c>
       <c r="R19" t="n">
-        <v>6790929</v>
+        <v>6790943</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2446,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131932725</v>
+        <v>131933367</v>
       </c>
       <c r="B20" t="n">
-        <v>79267</v>
+        <v>81254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,13 +2476,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465613</v>
+        <v>465599</v>
       </c>
       <c r="R20" t="n">
-        <v>6790943</v>
+        <v>6790901</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2543,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131933367</v>
+        <v>131932719</v>
       </c>
       <c r="B21" t="n">
-        <v>81252</v>
+        <v>57907</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,37 +2549,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465599</v>
+        <v>465613</v>
       </c>
       <c r="R21" t="n">
-        <v>6790901</v>
+        <v>6790943</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131931849</v>
+        <v>131928814</v>
       </c>
       <c r="B22" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465512</v>
+        <v>465357</v>
       </c>
       <c r="R22" t="n">
-        <v>6790845</v>
+        <v>6790909</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131928814</v>
+        <v>131931849</v>
       </c>
       <c r="B23" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465357</v>
+        <v>465512</v>
       </c>
       <c r="R23" t="n">
-        <v>6790909</v>
+        <v>6790845</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2837,7 +2837,7 @@
         <v>131933987</v>
       </c>
       <c r="B24" t="n">
-        <v>57905</v>
+        <v>57907</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131934622</v>
+        <v>131934170</v>
       </c>
       <c r="B25" t="n">
-        <v>79025</v>
+        <v>57907</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,37 +2947,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465369</v>
+        <v>465537</v>
       </c>
       <c r="R25" t="n">
-        <v>6790844</v>
+        <v>6790847</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3033,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131934170</v>
+        <v>131934622</v>
       </c>
       <c r="B26" t="n">
-        <v>57905</v>
+        <v>79027</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,42 +3049,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465537</v>
+        <v>465369</v>
       </c>
       <c r="R26" t="n">
-        <v>6790847</v>
+        <v>6790844</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131930993</v>
+        <v>131934405</v>
       </c>
       <c r="B27" t="n">
-        <v>83247</v>
+        <v>79269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,21 +3146,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465446</v>
+        <v>465402</v>
       </c>
       <c r="R27" t="n">
-        <v>6790876</v>
+        <v>6790848</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,11 +3206,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3237,49 +3232,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131931220</v>
+        <v>131930993</v>
       </c>
       <c r="B28" t="n">
-        <v>99045</v>
+        <v>83249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465472</v>
+        <v>465446</v>
       </c>
       <c r="R28" t="n">
-        <v>6790889</v>
+        <v>6790876</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3312,6 +3303,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3338,37 +3334,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131934382</v>
+        <v>131928811</v>
       </c>
       <c r="B29" t="n">
-        <v>99045</v>
+        <v>57904</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3377,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465402</v>
+        <v>465357</v>
       </c>
       <c r="R29" t="n">
-        <v>6790848</v>
+        <v>6790909</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3439,45 +3436,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131934405</v>
+        <v>131931220</v>
       </c>
       <c r="B30" t="n">
-        <v>79267</v>
+        <v>99047</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465402</v>
+        <v>465472</v>
       </c>
       <c r="R30" t="n">
-        <v>6790848</v>
+        <v>6790889</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3536,45 +3537,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131933651</v>
+        <v>131929195</v>
       </c>
       <c r="B31" t="n">
-        <v>79025</v>
+        <v>99047</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465592</v>
+        <v>465380</v>
       </c>
       <c r="R31" t="n">
-        <v>6790876</v>
+        <v>6790900</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3607,6 +3612,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3633,38 +3643,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131928811</v>
+        <v>131934382</v>
       </c>
       <c r="B32" t="n">
-        <v>57902</v>
+        <v>99047</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3673,10 +3682,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465357</v>
+        <v>465402</v>
       </c>
       <c r="R32" t="n">
-        <v>6790909</v>
+        <v>6790848</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,49 +3744,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131929195</v>
+        <v>131933651</v>
       </c>
       <c r="B33" t="n">
-        <v>99045</v>
+        <v>79027</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465380</v>
+        <v>465592</v>
       </c>
       <c r="R33" t="n">
-        <v>6790900</v>
+        <v>6790876</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3810,11 +3815,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3841,10 +3841,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131934129</v>
+        <v>131933749</v>
       </c>
       <c r="B34" t="n">
-        <v>79267</v>
+        <v>57907</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3852,37 +3852,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465537</v>
+        <v>465570</v>
       </c>
       <c r="R34" t="n">
-        <v>6790847</v>
+        <v>6790886</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3938,10 +3943,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131933749</v>
+        <v>131934634</v>
       </c>
       <c r="B35" t="n">
-        <v>57905</v>
+        <v>79888</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3949,39 +3954,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465570</v>
+        <v>465369</v>
       </c>
       <c r="R35" t="n">
-        <v>6790886</v>
+        <v>6790844</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4040,10 +4040,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131934557</v>
+        <v>131934641</v>
       </c>
       <c r="B36" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4137,10 +4137,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131934634</v>
+        <v>131934129</v>
       </c>
       <c r="B37" t="n">
-        <v>79886</v>
+        <v>79269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4148,21 +4148,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465369</v>
+        <v>465537</v>
       </c>
       <c r="R37" t="n">
-        <v>6790844</v>
+        <v>6790847</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4234,10 +4234,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131934709</v>
+        <v>131933369</v>
       </c>
       <c r="B38" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465369</v>
+        <v>465599</v>
       </c>
       <c r="R38" t="n">
-        <v>6790822</v>
+        <v>6790901</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4331,10 +4331,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131933369</v>
+        <v>131934709</v>
       </c>
       <c r="B39" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465599</v>
+        <v>465369</v>
       </c>
       <c r="R39" t="n">
-        <v>6790901</v>
+        <v>6790822</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
         <v>131933582</v>
       </c>
       <c r="B40" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>131934071</v>
       </c>
       <c r="B41" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>131930537</v>
       </c>
       <c r="B42" t="n">
-        <v>57905</v>
+        <v>57907</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>131926775</v>
       </c>
       <c r="B43" t="n">
-        <v>99045</v>
+        <v>99047</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4825,49 +4825,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131930390</v>
+        <v>131934704</v>
       </c>
       <c r="B44" t="n">
-        <v>99045</v>
+        <v>79027</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465346</v>
+        <v>465369</v>
       </c>
       <c r="R44" t="n">
-        <v>6790951</v>
+        <v>6790822</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4900,11 +4896,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4934,7 +4925,7 @@
         <v>131933829</v>
       </c>
       <c r="B45" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5028,10 +5019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934704</v>
+        <v>131926960</v>
       </c>
       <c r="B46" t="n">
-        <v>79025</v>
+        <v>79269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5039,21 +5030,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5063,13 +5054,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465369</v>
+        <v>465306</v>
       </c>
       <c r="R46" t="n">
-        <v>6790822</v>
+        <v>6790869</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5125,48 +5116,52 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131926960</v>
+        <v>131930390</v>
       </c>
       <c r="B47" t="n">
-        <v>79267</v>
+        <v>99047</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465306</v>
+        <v>465346</v>
       </c>
       <c r="R47" t="n">
-        <v>6790869</v>
+        <v>6790951</v>
       </c>
       <c r="S47" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5196,6 +5191,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131929040</v>
+        <v>131931514</v>
       </c>
       <c r="B48" t="n">
-        <v>92299</v>
+        <v>79269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465377</v>
+        <v>465508</v>
       </c>
       <c r="R48" t="n">
-        <v>6790886</v>
+        <v>6790896</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5319,10 +5319,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131926542</v>
+        <v>131930075</v>
       </c>
       <c r="B49" t="n">
-        <v>92299</v>
+        <v>99047</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5330,37 +5330,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465326</v>
+        <v>465351</v>
       </c>
       <c r="R49" t="n">
-        <v>6790884</v>
+        <v>6790929</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5390,11 +5394,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5421,10 +5420,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131930075</v>
+        <v>131929040</v>
       </c>
       <c r="B50" t="n">
-        <v>99045</v>
+        <v>92301</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,38 +5431,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465351</v>
+        <v>465377</v>
       </c>
       <c r="R50" t="n">
-        <v>6790929</v>
+        <v>6790886</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5522,32 +5517,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131931514</v>
+        <v>131926542</v>
       </c>
       <c r="B51" t="n">
-        <v>79267</v>
+        <v>92301</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5557,13 +5552,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465508</v>
+        <v>465326</v>
       </c>
       <c r="R51" t="n">
-        <v>6790896</v>
+        <v>6790884</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5593,6 +5588,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5619,38 +5619,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131933577</v>
+        <v>131930457</v>
       </c>
       <c r="B52" t="n">
-        <v>57905</v>
+        <v>99047</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5659,10 +5658,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465598</v>
+        <v>465359</v>
       </c>
       <c r="R52" t="n">
-        <v>6790885</v>
+        <v>6790942</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5695,6 +5694,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Många dolda under snön</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5721,37 +5725,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131930457</v>
+        <v>131933577</v>
       </c>
       <c r="B53" t="n">
-        <v>99045</v>
+        <v>57907</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5760,10 +5765,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465359</v>
+        <v>465598</v>
       </c>
       <c r="R53" t="n">
-        <v>6790942</v>
+        <v>6790885</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5796,11 +5801,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Många dolda under snön</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5827,10 +5827,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131928437</v>
+        <v>131934550</v>
       </c>
       <c r="B54" t="n">
-        <v>83247</v>
+        <v>57904</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5838,34 +5838,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465342</v>
+        <v>465369</v>
       </c>
       <c r="R54" t="n">
-        <v>6790888</v>
+        <v>6790844</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5898,11 +5903,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5929,10 +5929,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131927776</v>
+        <v>131934627</v>
       </c>
       <c r="B55" t="n">
-        <v>79267</v>
+        <v>79026</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5940,21 +5940,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465338</v>
+        <v>465369</v>
       </c>
       <c r="R55" t="n">
-        <v>6790853</v>
+        <v>6790844</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6026,10 +6026,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131934627</v>
+        <v>131926778</v>
       </c>
       <c r="B56" t="n">
-        <v>79024</v>
+        <v>79269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465369</v>
+        <v>465321</v>
       </c>
       <c r="R56" t="n">
-        <v>6790844</v>
+        <v>6790871</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131934550</v>
+        <v>131928437</v>
       </c>
       <c r="B57" t="n">
-        <v>57902</v>
+        <v>83249</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,39 +6134,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465369</v>
+        <v>465342</v>
       </c>
       <c r="R57" t="n">
-        <v>6790844</v>
+        <v>6790888</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6199,6 +6194,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6225,10 +6225,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131926778</v>
+        <v>131927776</v>
       </c>
       <c r="B58" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465321</v>
+        <v>465338</v>
       </c>
       <c r="R58" t="n">
-        <v>6790871</v>
+        <v>6790853</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6325,7 +6325,7 @@
         <v>131928063</v>
       </c>
       <c r="B59" t="n">
-        <v>58064</v>
+        <v>58066</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>131927394</v>
       </c>
       <c r="B60" t="n">
-        <v>83247</v>
+        <v>83249</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>131927401</v>
       </c>
       <c r="B61" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131926947</v>
+        <v>131928710</v>
       </c>
       <c r="B62" t="n">
-        <v>79886</v>
+        <v>79269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,13 +6653,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465306</v>
+        <v>465359</v>
       </c>
       <c r="R62" t="n">
-        <v>6790869</v>
+        <v>6790895</v>
       </c>
       <c r="S62" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6689,6 +6689,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6715,10 +6720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131928703</v>
+        <v>131932080</v>
       </c>
       <c r="B63" t="n">
-        <v>79024</v>
+        <v>79269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,21 +6731,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6750,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465359</v>
+        <v>465547</v>
       </c>
       <c r="R63" t="n">
-        <v>6790895</v>
+        <v>6790878</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6812,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131928710</v>
+        <v>131926947</v>
       </c>
       <c r="B64" t="n">
-        <v>79267</v>
+        <v>79888</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6823,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6847,13 +6852,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465359</v>
+        <v>465306</v>
       </c>
       <c r="R64" t="n">
-        <v>6790895</v>
+        <v>6790869</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6883,11 +6888,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6914,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131932080</v>
+        <v>131928703</v>
       </c>
       <c r="B65" t="n">
-        <v>79267</v>
+        <v>79026</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465547</v>
+        <v>465359</v>
       </c>
       <c r="R65" t="n">
-        <v>6790878</v>
+        <v>6790895</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7014,7 +7014,7 @@
         <v>131932078</v>
       </c>
       <c r="B66" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131927676</v>
+        <v>131930396</v>
       </c>
       <c r="B67" t="n">
-        <v>92299</v>
+        <v>79269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465330</v>
+        <v>465346</v>
       </c>
       <c r="R67" t="n">
-        <v>6790858</v>
+        <v>6790951</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,50 +7210,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131931509</v>
+        <v>131927676</v>
       </c>
       <c r="B68" t="n">
-        <v>57902</v>
+        <v>92301</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465508</v>
+        <v>465330</v>
       </c>
       <c r="R68" t="n">
-        <v>6790896</v>
+        <v>6790858</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7312,10 +7307,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131930396</v>
+        <v>131931509</v>
       </c>
       <c r="B69" t="n">
-        <v>79267</v>
+        <v>57904</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7323,34 +7318,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465346</v>
+        <v>465508</v>
       </c>
       <c r="R69" t="n">
-        <v>6790951</v>
+        <v>6790896</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7412,7 +7412,7 @@
         <v>131931743</v>
       </c>
       <c r="B70" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131926950</v>
+        <v>131926444</v>
       </c>
       <c r="B71" t="n">
-        <v>79857</v>
+        <v>79269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7517,21 +7517,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7541,13 +7541,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465306</v>
+        <v>465326</v>
       </c>
       <c r="R71" t="n">
-        <v>6790869</v>
+        <v>6790884</v>
       </c>
       <c r="S71" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7577,6 +7577,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7603,10 +7608,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131926444</v>
+        <v>131932356</v>
       </c>
       <c r="B72" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7638,13 +7643,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465326</v>
+        <v>465560</v>
       </c>
       <c r="R72" t="n">
-        <v>6790884</v>
+        <v>6790913</v>
       </c>
       <c r="S72" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7674,11 +7679,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7705,10 +7705,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131932356</v>
+        <v>131926950</v>
       </c>
       <c r="B73" t="n">
-        <v>79267</v>
+        <v>79859</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7716,21 +7716,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7740,13 +7740,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465560</v>
+        <v>465306</v>
       </c>
       <c r="R73" t="n">
-        <v>6790913</v>
+        <v>6790869</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>131970205</v>
       </c>
       <c r="B74" t="n">
-        <v>56475</v>
+        <v>56476</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131930995</v>
       </c>
       <c r="B2" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131933992</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131933662</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131929045</v>
       </c>
       <c r="B5" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131933929</v>
       </c>
       <c r="B6" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,48 +1160,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131930461</v>
+        <v>131932655</v>
       </c>
       <c r="B7" t="n">
-        <v>79269</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465359</v>
+        <v>465613</v>
       </c>
       <c r="R7" t="n">
-        <v>6790942</v>
+        <v>6790943</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,53 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131932655</v>
+        <v>131930461</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>79274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465613</v>
+        <v>465359</v>
       </c>
       <c r="R8" t="n">
-        <v>6790943</v>
+        <v>6790942</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131933121</v>
+        <v>131934127</v>
       </c>
       <c r="B9" t="n">
-        <v>79269</v>
+        <v>57909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,37 +1370,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465608</v>
+        <v>465537</v>
       </c>
       <c r="R9" t="n">
-        <v>6790896</v>
+        <v>6790847</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131933933</v>
+        <v>131927769</v>
       </c>
       <c r="B10" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,34 +1472,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465563</v>
+        <v>465338</v>
       </c>
       <c r="R10" t="n">
-        <v>6790864</v>
+        <v>6790853</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131931121</v>
+        <v>131933121</v>
       </c>
       <c r="B11" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,13 +1598,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465451</v>
+        <v>465608</v>
       </c>
       <c r="R11" t="n">
         <v>6790896</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1624,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131929201</v>
+        <v>131933933</v>
       </c>
       <c r="B12" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465380</v>
+        <v>465563</v>
       </c>
       <c r="R12" t="n">
-        <v>6790900</v>
+        <v>6790864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131928067</v>
+        <v>131931121</v>
       </c>
       <c r="B13" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465342</v>
+        <v>465451</v>
       </c>
       <c r="R13" t="n">
-        <v>6790879</v>
+        <v>6790896</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1823,6 +1828,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131934127</v>
+        <v>131929201</v>
       </c>
       <c r="B14" t="n">
-        <v>57904</v>
+        <v>79274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,42 +1870,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465537</v>
+        <v>465380</v>
       </c>
       <c r="R14" t="n">
-        <v>6790847</v>
+        <v>6790900</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1951,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131927769</v>
+        <v>131928067</v>
       </c>
       <c r="B15" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,42 +1967,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465338</v>
+        <v>465342</v>
       </c>
       <c r="R15" t="n">
-        <v>6790853</v>
+        <v>6790879</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131931225</v>
       </c>
       <c r="B16" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>131931931</v>
       </c>
       <c r="B17" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131930082</v>
+        <v>131933367</v>
       </c>
       <c r="B18" t="n">
-        <v>79269</v>
+        <v>81259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465351</v>
+        <v>465599</v>
       </c>
       <c r="R18" t="n">
-        <v>6790929</v>
+        <v>6790901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131932725</v>
+        <v>131932719</v>
       </c>
       <c r="B19" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,24 +2355,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -2441,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131933367</v>
+        <v>131930082</v>
       </c>
       <c r="B20" t="n">
-        <v>81254</v>
+        <v>79274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465599</v>
+        <v>465351</v>
       </c>
       <c r="R20" t="n">
-        <v>6790901</v>
+        <v>6790929</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131932719</v>
+        <v>131932725</v>
       </c>
       <c r="B21" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,29 +2554,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -2643,7 +2643,7 @@
         <v>131928814</v>
       </c>
       <c r="B22" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>131931849</v>
       </c>
       <c r="B23" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>131933987</v>
       </c>
       <c r="B24" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>131934170</v>
       </c>
       <c r="B25" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>131934622</v>
       </c>
       <c r="B26" t="n">
-        <v>79027</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131934405</v>
+        <v>131928811</v>
       </c>
       <c r="B27" t="n">
-        <v>79269</v>
+        <v>57909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,34 +3146,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465402</v>
+        <v>465357</v>
       </c>
       <c r="R27" t="n">
-        <v>6790848</v>
+        <v>6790909</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,45 +3237,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131930993</v>
+        <v>131929195</v>
       </c>
       <c r="B28" t="n">
-        <v>83249</v>
+        <v>99052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465446</v>
+        <v>465380</v>
       </c>
       <c r="R28" t="n">
-        <v>6790876</v>
+        <v>6790900</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3307,7 +3316,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3334,10 +3343,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131928811</v>
+        <v>131934405</v>
       </c>
       <c r="B29" t="n">
-        <v>57904</v>
+        <v>79274</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3345,39 +3354,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465357</v>
+        <v>465402</v>
       </c>
       <c r="R29" t="n">
-        <v>6790909</v>
+        <v>6790848</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3436,49 +3440,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131931220</v>
+        <v>131930993</v>
       </c>
       <c r="B30" t="n">
-        <v>99047</v>
+        <v>83254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465472</v>
+        <v>465446</v>
       </c>
       <c r="R30" t="n">
-        <v>6790889</v>
+        <v>6790876</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3511,6 +3511,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3537,10 +3542,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131929195</v>
+        <v>131931220</v>
       </c>
       <c r="B31" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3567,7 +3572,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>140</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3576,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465380</v>
+        <v>465472</v>
       </c>
       <c r="R31" t="n">
-        <v>6790900</v>
+        <v>6790889</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3612,11 +3617,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3646,7 +3646,7 @@
         <v>131934382</v>
       </c>
       <c r="B32" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>131933651</v>
       </c>
       <c r="B33" t="n">
-        <v>79027</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131933749</v>
+        <v>131934634</v>
       </c>
       <c r="B34" t="n">
-        <v>57907</v>
+        <v>79893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3852,39 +3852,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465570</v>
+        <v>465369</v>
       </c>
       <c r="R34" t="n">
-        <v>6790886</v>
+        <v>6790844</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3943,10 +3938,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131934634</v>
+        <v>131934641</v>
       </c>
       <c r="B35" t="n">
-        <v>79888</v>
+        <v>79274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3954,21 +3949,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4040,10 +4035,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131934641</v>
+        <v>131934129</v>
       </c>
       <c r="B36" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,13 +4070,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465369</v>
+        <v>465537</v>
       </c>
       <c r="R36" t="n">
-        <v>6790844</v>
+        <v>6790847</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4137,10 +4132,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131934129</v>
+        <v>131933369</v>
       </c>
       <c r="B37" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,13 +4167,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465537</v>
+        <v>465599</v>
       </c>
       <c r="R37" t="n">
-        <v>6790847</v>
+        <v>6790901</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4234,10 +4229,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131933369</v>
+        <v>131934709</v>
       </c>
       <c r="B38" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465599</v>
+        <v>465369</v>
       </c>
       <c r="R38" t="n">
-        <v>6790901</v>
+        <v>6790822</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4331,10 +4326,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131934709</v>
+        <v>131933749</v>
       </c>
       <c r="B39" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4342,34 +4337,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465369</v>
+        <v>465570</v>
       </c>
       <c r="R39" t="n">
-        <v>6790822</v>
+        <v>6790886</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
         <v>131933582</v>
       </c>
       <c r="B40" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>131934071</v>
       </c>
       <c r="B41" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>131930537</v>
       </c>
       <c r="B42" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>131926775</v>
       </c>
       <c r="B43" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4825,10 +4825,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131934704</v>
+        <v>131933829</v>
       </c>
       <c r="B44" t="n">
-        <v>79027</v>
+        <v>79274</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4836,21 +4836,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465369</v>
+        <v>465570</v>
       </c>
       <c r="R44" t="n">
-        <v>6790822</v>
+        <v>6790886</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4922,10 +4922,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131933829</v>
+        <v>131926960</v>
       </c>
       <c r="B45" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465570</v>
+        <v>465306</v>
       </c>
       <c r="R45" t="n">
-        <v>6790886</v>
+        <v>6790869</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5019,48 +5019,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131926960</v>
+        <v>131930390</v>
       </c>
       <c r="B46" t="n">
-        <v>79269</v>
+        <v>99052</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465306</v>
+        <v>465346</v>
       </c>
       <c r="R46" t="n">
-        <v>6790869</v>
+        <v>6790951</v>
       </c>
       <c r="S46" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5090,6 +5094,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5116,49 +5125,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131930390</v>
+        <v>131934704</v>
       </c>
       <c r="B47" t="n">
-        <v>99047</v>
+        <v>79032</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465346</v>
+        <v>465369</v>
       </c>
       <c r="R47" t="n">
-        <v>6790951</v>
+        <v>6790822</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5191,11 +5196,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5222,45 +5222,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131931514</v>
+        <v>131930075</v>
       </c>
       <c r="B48" t="n">
-        <v>79269</v>
+        <v>99052</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465508</v>
+        <v>465351</v>
       </c>
       <c r="R48" t="n">
-        <v>6790896</v>
+        <v>6790929</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5319,49 +5323,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131930075</v>
+        <v>131931514</v>
       </c>
       <c r="B49" t="n">
-        <v>99047</v>
+        <v>79274</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465351</v>
+        <v>465508</v>
       </c>
       <c r="R49" t="n">
-        <v>6790929</v>
+        <v>6790896</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5423,7 +5423,7 @@
         <v>131929040</v>
       </c>
       <c r="B50" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>131926542</v>
       </c>
       <c r="B51" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5619,37 +5619,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131930457</v>
+        <v>131933577</v>
       </c>
       <c r="B52" t="n">
-        <v>99047</v>
+        <v>57912</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5658,10 +5659,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465359</v>
+        <v>465598</v>
       </c>
       <c r="R52" t="n">
-        <v>6790942</v>
+        <v>6790885</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5694,11 +5695,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Många dolda under snön</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5725,38 +5721,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131933577</v>
+        <v>131930457</v>
       </c>
       <c r="B53" t="n">
-        <v>57907</v>
+        <v>99052</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5765,10 +5760,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465598</v>
+        <v>465359</v>
       </c>
       <c r="R53" t="n">
-        <v>6790885</v>
+        <v>6790942</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5801,6 +5796,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Många dolda under snön</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5830,7 +5830,7 @@
         <v>131934550</v>
       </c>
       <c r="B54" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>131934627</v>
       </c>
       <c r="B55" t="n">
-        <v>79026</v>
+        <v>79031</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>131926778</v>
       </c>
       <c r="B56" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>131928437</v>
       </c>
       <c r="B57" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>131927776</v>
       </c>
       <c r="B58" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131928063</v>
+        <v>131927394</v>
       </c>
       <c r="B59" t="n">
-        <v>58066</v>
+        <v>83254</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,42 +6333,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465342</v>
+        <v>465330</v>
       </c>
       <c r="R59" t="n">
-        <v>6790879</v>
+        <v>6790858</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6424,10 +6419,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131927394</v>
+        <v>131927401</v>
       </c>
       <c r="B60" t="n">
-        <v>83249</v>
+        <v>79274</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6435,21 +6430,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6521,10 +6516,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131927401</v>
+        <v>131928063</v>
       </c>
       <c r="B61" t="n">
-        <v>79269</v>
+        <v>58071</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,37 +6527,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465330</v>
+        <v>465342</v>
       </c>
       <c r="R61" t="n">
-        <v>6790858</v>
+        <v>6790879</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131928710</v>
+        <v>131932078</v>
       </c>
       <c r="B62" t="n">
-        <v>79269</v>
+        <v>57909</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,34 +6629,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465359</v>
+        <v>465547</v>
       </c>
       <c r="R62" t="n">
-        <v>6790895</v>
+        <v>6790878</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6689,11 +6694,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6720,10 +6720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131932080</v>
+        <v>131928710</v>
       </c>
       <c r="B63" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465547</v>
+        <v>465359</v>
       </c>
       <c r="R63" t="n">
-        <v>6790878</v>
+        <v>6790895</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6791,6 +6791,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6817,10 +6822,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131926947</v>
+        <v>131932080</v>
       </c>
       <c r="B64" t="n">
-        <v>79888</v>
+        <v>79274</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,21 +6833,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6852,13 +6857,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465306</v>
+        <v>465547</v>
       </c>
       <c r="R64" t="n">
-        <v>6790869</v>
+        <v>6790878</v>
       </c>
       <c r="S64" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6914,10 +6919,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131928703</v>
+        <v>131926947</v>
       </c>
       <c r="B65" t="n">
-        <v>79026</v>
+        <v>79893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6930,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,13 +6954,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465359</v>
+        <v>465306</v>
       </c>
       <c r="R65" t="n">
-        <v>6790895</v>
+        <v>6790869</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7011,10 +7016,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131932078</v>
+        <v>131928703</v>
       </c>
       <c r="B66" t="n">
-        <v>57904</v>
+        <v>79031</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7022,39 +7027,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465547</v>
+        <v>465359</v>
       </c>
       <c r="R66" t="n">
-        <v>6790878</v>
+        <v>6790895</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131930396</v>
+        <v>131927676</v>
       </c>
       <c r="B67" t="n">
-        <v>79269</v>
+        <v>92306</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465346</v>
+        <v>465330</v>
       </c>
       <c r="R67" t="n">
-        <v>6790951</v>
+        <v>6790858</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,32 +7210,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131927676</v>
+        <v>131930396</v>
       </c>
       <c r="B68" t="n">
-        <v>92301</v>
+        <v>79274</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7245,10 +7245,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465330</v>
+        <v>465346</v>
       </c>
       <c r="R68" t="n">
-        <v>6790858</v>
+        <v>6790951</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7310,7 +7310,7 @@
         <v>131931509</v>
       </c>
       <c r="B69" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>131931743</v>
       </c>
       <c r="B70" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>131926444</v>
       </c>
       <c r="B71" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>131932356</v>
       </c>
       <c r="B72" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>131926950</v>
       </c>
       <c r="B73" t="n">
-        <v>79859</v>
+        <v>79864</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>131970205</v>
       </c>
       <c r="B74" t="n">
-        <v>56476</v>
+        <v>56481</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -1160,53 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131932655</v>
+        <v>131930461</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>79274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465613</v>
+        <v>465359</v>
       </c>
       <c r="R7" t="n">
-        <v>6790943</v>
+        <v>6790942</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1262,48 +1257,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131930461</v>
+        <v>131932655</v>
       </c>
       <c r="B8" t="n">
-        <v>79274</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465359</v>
+        <v>465613</v>
       </c>
       <c r="R8" t="n">
-        <v>6790942</v>
+        <v>6790943</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131933367</v>
+        <v>131930082</v>
       </c>
       <c r="B18" t="n">
-        <v>81259</v>
+        <v>79274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465599</v>
+        <v>465351</v>
       </c>
       <c r="R18" t="n">
-        <v>6790901</v>
+        <v>6790929</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131932719</v>
+        <v>131932725</v>
       </c>
       <c r="B19" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,29 +2355,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -2446,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131930082</v>
+        <v>131933367</v>
       </c>
       <c r="B20" t="n">
-        <v>79274</v>
+        <v>81259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465351</v>
+        <v>465599</v>
       </c>
       <c r="R20" t="n">
-        <v>6790929</v>
+        <v>6790901</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2543,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131932725</v>
+        <v>131932719</v>
       </c>
       <c r="B21" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,24 +2549,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131928814</v>
+        <v>131933987</v>
       </c>
       <c r="B22" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,34 +2651,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465357</v>
+        <v>465558</v>
       </c>
       <c r="R22" t="n">
-        <v>6790909</v>
+        <v>6790843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131931849</v>
+        <v>131934170</v>
       </c>
       <c r="B23" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,37 +2753,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465512</v>
+        <v>465537</v>
       </c>
       <c r="R23" t="n">
-        <v>6790845</v>
+        <v>6790847</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2834,10 +2844,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131933987</v>
+        <v>131934622</v>
       </c>
       <c r="B24" t="n">
-        <v>57912</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,39 +2855,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465558</v>
+        <v>465369</v>
       </c>
       <c r="R24" t="n">
-        <v>6790843</v>
+        <v>6790844</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131934170</v>
+        <v>131928814</v>
       </c>
       <c r="B25" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,42 +2952,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465537</v>
+        <v>465357</v>
       </c>
       <c r="R25" t="n">
-        <v>6790847</v>
+        <v>6790909</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131934622</v>
+        <v>131931849</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79274</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465369</v>
+        <v>465512</v>
       </c>
       <c r="R26" t="n">
-        <v>6790844</v>
+        <v>6790845</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -5222,49 +5222,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131930075</v>
+        <v>131931514</v>
       </c>
       <c r="B48" t="n">
-        <v>99052</v>
+        <v>79274</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465351</v>
+        <v>465508</v>
       </c>
       <c r="R48" t="n">
-        <v>6790929</v>
+        <v>6790896</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5323,32 +5319,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131931514</v>
+        <v>131929040</v>
       </c>
       <c r="B49" t="n">
-        <v>79274</v>
+        <v>92306</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5358,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465508</v>
+        <v>465377</v>
       </c>
       <c r="R49" t="n">
-        <v>6790896</v>
+        <v>6790886</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5420,7 +5416,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131929040</v>
+        <v>131926542</v>
       </c>
       <c r="B50" t="n">
         <v>92306</v>
@@ -5455,13 +5451,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465377</v>
+        <v>465326</v>
       </c>
       <c r="R50" t="n">
-        <v>6790886</v>
+        <v>6790884</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5491,6 +5487,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5517,10 +5518,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131926542</v>
+        <v>131930075</v>
       </c>
       <c r="B51" t="n">
-        <v>92306</v>
+        <v>99052</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5528,37 +5529,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465326</v>
+        <v>465351</v>
       </c>
       <c r="R51" t="n">
-        <v>6790884</v>
+        <v>6790929</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5588,11 +5593,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7113,32 +7113,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131927676</v>
+        <v>131930396</v>
       </c>
       <c r="B67" t="n">
-        <v>92306</v>
+        <v>79274</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465330</v>
+        <v>465346</v>
       </c>
       <c r="R67" t="n">
-        <v>6790858</v>
+        <v>6790951</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,10 +7210,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131930396</v>
+        <v>131931509</v>
       </c>
       <c r="B68" t="n">
-        <v>79274</v>
+        <v>57909</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7221,34 +7221,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465346</v>
+        <v>465508</v>
       </c>
       <c r="R68" t="n">
-        <v>6790951</v>
+        <v>6790896</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7307,50 +7312,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131931509</v>
+        <v>131927676</v>
       </c>
       <c r="B69" t="n">
-        <v>57909</v>
+        <v>92306</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465508</v>
+        <v>465330</v>
       </c>
       <c r="R69" t="n">
-        <v>6790896</v>
+        <v>6790858</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131930995</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131933992</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131933662</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131929045</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131933929</v>
       </c>
       <c r="B6" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>131930461</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>131932655</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>57906</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131934127</v>
+        <v>131927769</v>
       </c>
       <c r="B9" t="n">
-        <v>57909</v>
+        <v>57914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1390,7 +1390,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465537</v>
+        <v>465338</v>
       </c>
       <c r="R9" t="n">
-        <v>6790847</v>
+        <v>6790853</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131927769</v>
+        <v>131934127</v>
       </c>
       <c r="B10" t="n">
-        <v>57912</v>
+        <v>57911</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465338</v>
+        <v>465537</v>
       </c>
       <c r="R10" t="n">
-        <v>6790853</v>
+        <v>6790847</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>131933121</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>131933933</v>
       </c>
       <c r="B12" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>131931121</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>131929201</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>131928067</v>
       </c>
       <c r="B15" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131931225</v>
       </c>
       <c r="B16" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>131931931</v>
       </c>
       <c r="B17" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131930082</v>
+        <v>131933367</v>
       </c>
       <c r="B18" t="n">
-        <v>79274</v>
+        <v>81261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465351</v>
+        <v>465599</v>
       </c>
       <c r="R18" t="n">
-        <v>6790929</v>
+        <v>6790901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131932725</v>
+        <v>131930082</v>
       </c>
       <c r="B19" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465613</v>
+        <v>465351</v>
       </c>
       <c r="R19" t="n">
-        <v>6790943</v>
+        <v>6790929</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131933367</v>
+        <v>131932725</v>
       </c>
       <c r="B20" t="n">
-        <v>81259</v>
+        <v>79276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465599</v>
+        <v>465613</v>
       </c>
       <c r="R20" t="n">
-        <v>6790901</v>
+        <v>6790943</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>131932719</v>
       </c>
       <c r="B21" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131933987</v>
+        <v>131928814</v>
       </c>
       <c r="B22" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,39 +2651,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465558</v>
+        <v>465357</v>
       </c>
       <c r="R22" t="n">
-        <v>6790843</v>
+        <v>6790909</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131934170</v>
+        <v>131931849</v>
       </c>
       <c r="B23" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,42 +2748,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465537</v>
+        <v>465512</v>
       </c>
       <c r="R23" t="n">
-        <v>6790847</v>
+        <v>6790845</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2844,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131934622</v>
+        <v>131933987</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>57914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2855,34 +2845,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465369</v>
+        <v>465558</v>
       </c>
       <c r="R24" t="n">
-        <v>6790844</v>
+        <v>6790843</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2941,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131928814</v>
+        <v>131934170</v>
       </c>
       <c r="B25" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,37 +2947,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465357</v>
+        <v>465537</v>
       </c>
       <c r="R25" t="n">
-        <v>6790909</v>
+        <v>6790847</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131931849</v>
+        <v>131934622</v>
       </c>
       <c r="B26" t="n">
-        <v>79274</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465512</v>
+        <v>465369</v>
       </c>
       <c r="R26" t="n">
-        <v>6790845</v>
+        <v>6790844</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131928811</v>
+        <v>131934405</v>
       </c>
       <c r="B27" t="n">
-        <v>57909</v>
+        <v>79276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,39 +3146,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465357</v>
+        <v>465402</v>
       </c>
       <c r="R27" t="n">
-        <v>6790909</v>
+        <v>6790848</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,49 +3232,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131929195</v>
+        <v>131930993</v>
       </c>
       <c r="B28" t="n">
-        <v>99052</v>
+        <v>83256</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465380</v>
+        <v>465446</v>
       </c>
       <c r="R28" t="n">
-        <v>6790900</v>
+        <v>6790876</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3316,7 +3307,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ca 80 synliga där snön försvunnit</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3343,10 +3334,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131934405</v>
+        <v>131928811</v>
       </c>
       <c r="B29" t="n">
-        <v>79274</v>
+        <v>57911</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3354,34 +3345,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465402</v>
+        <v>465357</v>
       </c>
       <c r="R29" t="n">
-        <v>6790848</v>
+        <v>6790909</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3440,45 +3436,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131930993</v>
+        <v>131931220</v>
       </c>
       <c r="B30" t="n">
-        <v>83254</v>
+        <v>99054</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465446</v>
+        <v>465472</v>
       </c>
       <c r="R30" t="n">
-        <v>6790876</v>
+        <v>6790889</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3511,11 +3511,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3542,10 +3537,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131931220</v>
+        <v>131929195</v>
       </c>
       <c r="B31" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3572,7 +3567,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3581,10 +3576,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465472</v>
+        <v>465380</v>
       </c>
       <c r="R31" t="n">
-        <v>6790889</v>
+        <v>6790900</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3617,6 +3612,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3646,7 +3646,7 @@
         <v>131934382</v>
       </c>
       <c r="B32" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>131933651</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>131934634</v>
       </c>
       <c r="B34" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>131934641</v>
       </c>
       <c r="B35" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>131934129</v>
       </c>
       <c r="B36" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>131933369</v>
       </c>
       <c r="B37" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>131934709</v>
       </c>
       <c r="B38" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>131933749</v>
       </c>
       <c r="B39" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>131933582</v>
       </c>
       <c r="B40" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4525,45 +4525,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131934071</v>
+        <v>131926775</v>
       </c>
       <c r="B41" t="n">
-        <v>79274</v>
+        <v>99054</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465575</v>
+        <v>465321</v>
       </c>
       <c r="R41" t="n">
-        <v>6790844</v>
+        <v>6790871</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4622,10 +4626,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131930537</v>
+        <v>131934071</v>
       </c>
       <c r="B42" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4633,39 +4637,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465357</v>
+        <v>465575</v>
       </c>
       <c r="R42" t="n">
-        <v>6790909</v>
+        <v>6790844</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4724,37 +4723,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131926775</v>
+        <v>131930537</v>
       </c>
       <c r="B43" t="n">
-        <v>99052</v>
+        <v>57914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>260</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465321</v>
+        <v>465357</v>
       </c>
       <c r="R43" t="n">
-        <v>6790871</v>
+        <v>6790909</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4825,45 +4825,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131933829</v>
+        <v>131930390</v>
       </c>
       <c r="B44" t="n">
-        <v>79274</v>
+        <v>99054</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465570</v>
+        <v>465346</v>
       </c>
       <c r="R44" t="n">
-        <v>6790886</v>
+        <v>6790951</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4896,6 +4900,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4922,10 +4931,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131926960</v>
+        <v>131933829</v>
       </c>
       <c r="B45" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,13 +4966,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465306</v>
+        <v>465570</v>
       </c>
       <c r="R45" t="n">
-        <v>6790869</v>
+        <v>6790886</v>
       </c>
       <c r="S45" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5019,52 +5028,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131930390</v>
+        <v>131926960</v>
       </c>
       <c r="B46" t="n">
-        <v>99052</v>
+        <v>79276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465346</v>
+        <v>465306</v>
       </c>
       <c r="R46" t="n">
-        <v>6790951</v>
+        <v>6790869</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5094,11 +5099,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5128,7 +5128,7 @@
         <v>131934704</v>
       </c>
       <c r="B47" t="n">
-        <v>79032</v>
+        <v>79034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5222,45 +5222,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131931514</v>
+        <v>131930075</v>
       </c>
       <c r="B48" t="n">
-        <v>79274</v>
+        <v>99054</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465508</v>
+        <v>465351</v>
       </c>
       <c r="R48" t="n">
-        <v>6790896</v>
+        <v>6790929</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5322,7 +5326,7 @@
         <v>131929040</v>
       </c>
       <c r="B49" t="n">
-        <v>92306</v>
+        <v>92308</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5419,7 +5423,7 @@
         <v>131926542</v>
       </c>
       <c r="B50" t="n">
-        <v>92306</v>
+        <v>92308</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5518,49 +5522,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131930075</v>
+        <v>131931514</v>
       </c>
       <c r="B51" t="n">
-        <v>99052</v>
+        <v>79276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465351</v>
+        <v>465508</v>
       </c>
       <c r="R51" t="n">
-        <v>6790929</v>
+        <v>6790896</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5619,38 +5619,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131933577</v>
+        <v>131930457</v>
       </c>
       <c r="B52" t="n">
-        <v>57912</v>
+        <v>99054</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5659,10 +5658,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465598</v>
+        <v>465359</v>
       </c>
       <c r="R52" t="n">
-        <v>6790885</v>
+        <v>6790942</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5695,6 +5694,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Många dolda under snön</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5721,37 +5725,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131930457</v>
+        <v>131933577</v>
       </c>
       <c r="B53" t="n">
-        <v>99052</v>
+        <v>57914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5760,10 +5765,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465359</v>
+        <v>465598</v>
       </c>
       <c r="R53" t="n">
-        <v>6790942</v>
+        <v>6790885</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5796,11 +5801,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Många dolda under snön</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5827,10 +5827,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131934550</v>
+        <v>131934627</v>
       </c>
       <c r="B54" t="n">
-        <v>57909</v>
+        <v>79033</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5838,29 +5838,24 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -5929,10 +5924,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131934627</v>
+        <v>131926778</v>
       </c>
       <c r="B55" t="n">
-        <v>79031</v>
+        <v>79276</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5940,21 +5935,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5964,10 +5959,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465369</v>
+        <v>465321</v>
       </c>
       <c r="R55" t="n">
-        <v>6790844</v>
+        <v>6790871</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6026,10 +6021,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131926778</v>
+        <v>131928437</v>
       </c>
       <c r="B56" t="n">
-        <v>79274</v>
+        <v>83256</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6037,21 +6032,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6061,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465321</v>
+        <v>465342</v>
       </c>
       <c r="R56" t="n">
-        <v>6790871</v>
+        <v>6790888</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6097,6 +6092,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131928437</v>
+        <v>131927776</v>
       </c>
       <c r="B57" t="n">
-        <v>83254</v>
+        <v>79276</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465342</v>
+        <v>465338</v>
       </c>
       <c r="R57" t="n">
-        <v>6790888</v>
+        <v>6790853</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,11 +6194,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6225,10 +6220,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131927776</v>
+        <v>131934550</v>
       </c>
       <c r="B58" t="n">
-        <v>79274</v>
+        <v>57911</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6236,34 +6231,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465338</v>
+        <v>465369</v>
       </c>
       <c r="R58" t="n">
-        <v>6790853</v>
+        <v>6790844</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6325,7 +6325,7 @@
         <v>131927394</v>
       </c>
       <c r="B59" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>131927401</v>
       </c>
       <c r="B60" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>131928063</v>
       </c>
       <c r="B61" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131932078</v>
+        <v>131928710</v>
       </c>
       <c r="B62" t="n">
-        <v>57909</v>
+        <v>79276</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,39 +6629,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465547</v>
+        <v>465359</v>
       </c>
       <c r="R62" t="n">
-        <v>6790878</v>
+        <v>6790895</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6694,6 +6689,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6720,10 +6720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131928710</v>
+        <v>131932080</v>
       </c>
       <c r="B63" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465359</v>
+        <v>465547</v>
       </c>
       <c r="R63" t="n">
-        <v>6790895</v>
+        <v>6790878</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6791,11 +6791,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6822,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131932080</v>
+        <v>131926947</v>
       </c>
       <c r="B64" t="n">
-        <v>79274</v>
+        <v>79895</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6833,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6857,13 +6852,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465547</v>
+        <v>465306</v>
       </c>
       <c r="R64" t="n">
-        <v>6790878</v>
+        <v>6790869</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6919,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131926947</v>
+        <v>131928703</v>
       </c>
       <c r="B65" t="n">
-        <v>79893</v>
+        <v>79033</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6930,21 +6925,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6954,13 +6949,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465306</v>
+        <v>465359</v>
       </c>
       <c r="R65" t="n">
-        <v>6790869</v>
+        <v>6790895</v>
       </c>
       <c r="S65" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7016,10 +7011,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131928703</v>
+        <v>131932078</v>
       </c>
       <c r="B66" t="n">
-        <v>79031</v>
+        <v>57911</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7027,34 +7022,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465359</v>
+        <v>465547</v>
       </c>
       <c r="R66" t="n">
-        <v>6790895</v>
+        <v>6790878</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131930396</v>
+        <v>131931509</v>
       </c>
       <c r="B67" t="n">
-        <v>79274</v>
+        <v>57911</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7124,34 +7124,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465346</v>
+        <v>465508</v>
       </c>
       <c r="R67" t="n">
-        <v>6790951</v>
+        <v>6790896</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,50 +7215,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131931509</v>
+        <v>131927676</v>
       </c>
       <c r="B68" t="n">
-        <v>57909</v>
+        <v>92308</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465508</v>
+        <v>465330</v>
       </c>
       <c r="R68" t="n">
-        <v>6790896</v>
+        <v>6790858</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7312,32 +7312,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131927676</v>
+        <v>131930396</v>
       </c>
       <c r="B69" t="n">
-        <v>92306</v>
+        <v>79276</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465330</v>
+        <v>465346</v>
       </c>
       <c r="R69" t="n">
-        <v>6790858</v>
+        <v>6790951</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7412,7 +7412,7 @@
         <v>131931743</v>
       </c>
       <c r="B70" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>131926444</v>
       </c>
       <c r="B71" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>131932356</v>
       </c>
       <c r="B72" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>131926950</v>
       </c>
       <c r="B73" t="n">
-        <v>79864</v>
+        <v>79866</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>131970205</v>
       </c>
       <c r="B74" t="n">
-        <v>56481</v>
+        <v>56483</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131930995</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131933992</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131933929</v>
+        <v>131933662</v>
       </c>
       <c r="B4" t="n">
-        <v>97960</v>
+        <v>79317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465563</v>
+        <v>465592</v>
       </c>
       <c r="R4" t="n">
-        <v>6790864</v>
+        <v>6790876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131933662</v>
+        <v>131929045</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465592</v>
+        <v>465377</v>
       </c>
       <c r="R5" t="n">
-        <v>6790876</v>
+        <v>6790886</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131929045</v>
+        <v>131933929</v>
       </c>
       <c r="B6" t="n">
-        <v>79315</v>
+        <v>97963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465377</v>
+        <v>465563</v>
       </c>
       <c r="R6" t="n">
-        <v>6790886</v>
+        <v>6790864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,53 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131932655</v>
+        <v>131930461</v>
       </c>
       <c r="B7" t="n">
-        <v>57940</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465613</v>
+        <v>465359</v>
       </c>
       <c r="R7" t="n">
-        <v>6790943</v>
+        <v>6790942</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1262,48 +1257,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131930461</v>
+        <v>131932655</v>
       </c>
       <c r="B8" t="n">
-        <v>79315</v>
+        <v>57940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465359</v>
+        <v>465613</v>
       </c>
       <c r="R8" t="n">
-        <v>6790942</v>
+        <v>6790943</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>131933121</v>
       </c>
       <c r="B10" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>131933933</v>
       </c>
       <c r="B11" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>131931121</v>
       </c>
       <c r="B12" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>131929201</v>
       </c>
       <c r="B13" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>131928067</v>
       </c>
       <c r="B14" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131931225</v>
       </c>
       <c r="B16" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>131931931</v>
       </c>
       <c r="B17" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131930082</v>
+        <v>131933367</v>
       </c>
       <c r="B18" t="n">
-        <v>79315</v>
+        <v>81302</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465351</v>
+        <v>465599</v>
       </c>
       <c r="R18" t="n">
-        <v>6790929</v>
+        <v>6790901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131932725</v>
+        <v>131930082</v>
       </c>
       <c r="B19" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465613</v>
+        <v>465351</v>
       </c>
       <c r="R19" t="n">
-        <v>6790943</v>
+        <v>6790929</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131932719</v>
+        <v>131932725</v>
       </c>
       <c r="B20" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,29 +2452,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -2543,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131933367</v>
+        <v>131932719</v>
       </c>
       <c r="B21" t="n">
-        <v>81300</v>
+        <v>57948</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,37 +2549,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465599</v>
+        <v>465613</v>
       </c>
       <c r="R21" t="n">
-        <v>6790901</v>
+        <v>6790943</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>131928814</v>
       </c>
       <c r="B22" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>131931849</v>
       </c>
       <c r="B23" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2834,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131933987</v>
+        <v>131934622</v>
       </c>
       <c r="B24" t="n">
-        <v>57948</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,39 +2845,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465558</v>
+        <v>465369</v>
       </c>
       <c r="R24" t="n">
-        <v>6790843</v>
+        <v>6790844</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,7 +2931,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131934170</v>
+        <v>131933987</v>
       </c>
       <c r="B25" t="n">
         <v>57948</v>
@@ -2976,13 +2971,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465537</v>
+        <v>465558</v>
       </c>
       <c r="R25" t="n">
-        <v>6790847</v>
+        <v>6790843</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3038,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131934622</v>
+        <v>131934170</v>
       </c>
       <c r="B26" t="n">
-        <v>79073</v>
+        <v>57948</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3049,37 +3044,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465369</v>
+        <v>465537</v>
       </c>
       <c r="R26" t="n">
-        <v>6790844</v>
+        <v>6790847</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131928811</v>
+        <v>131934405</v>
       </c>
       <c r="B27" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,39 +3146,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465357</v>
+        <v>465402</v>
       </c>
       <c r="R27" t="n">
-        <v>6790909</v>
+        <v>6790848</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,10 +3232,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131933651</v>
+        <v>131930993</v>
       </c>
       <c r="B28" t="n">
-        <v>79073</v>
+        <v>83297</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3248,21 +3243,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3272,7 +3267,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465592</v>
+        <v>465446</v>
       </c>
       <c r="R28" t="n">
         <v>6790876</v>
@@ -3308,6 +3303,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3334,10 +3334,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131934405</v>
+        <v>131928811</v>
       </c>
       <c r="B29" t="n">
-        <v>79315</v>
+        <v>57945</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3345,34 +3345,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465402</v>
+        <v>465357</v>
       </c>
       <c r="R29" t="n">
-        <v>6790848</v>
+        <v>6790909</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,45 +3436,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131930993</v>
+        <v>131931220</v>
       </c>
       <c r="B30" t="n">
-        <v>83295</v>
+        <v>99098</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465446</v>
+        <v>465472</v>
       </c>
       <c r="R30" t="n">
-        <v>6790876</v>
+        <v>6790889</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,11 +3511,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3533,10 +3537,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131931220</v>
+        <v>131929195</v>
       </c>
       <c r="B31" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3563,7 +3567,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3572,10 +3576,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465472</v>
+        <v>465380</v>
       </c>
       <c r="R31" t="n">
-        <v>6790889</v>
+        <v>6790900</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3608,6 +3612,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3634,10 +3643,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131929195</v>
+        <v>131934382</v>
       </c>
       <c r="B32" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3664,7 +3673,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3673,10 +3682,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465380</v>
+        <v>465402</v>
       </c>
       <c r="R32" t="n">
-        <v>6790900</v>
+        <v>6790848</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3709,11 +3718,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3740,49 +3744,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131934382</v>
+        <v>131933651</v>
       </c>
       <c r="B33" t="n">
-        <v>99095</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465402</v>
+        <v>465592</v>
       </c>
       <c r="R33" t="n">
-        <v>6790848</v>
+        <v>6790876</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3844,7 +3844,7 @@
         <v>131934634</v>
       </c>
       <c r="B34" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>131934641</v>
       </c>
       <c r="B35" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>131934129</v>
       </c>
       <c r="B36" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>131933369</v>
       </c>
       <c r="B37" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>131934709</v>
       </c>
       <c r="B38" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>131933582</v>
       </c>
       <c r="B40" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4525,38 +4525,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131930537</v>
+        <v>131926775</v>
       </c>
       <c r="B41" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>260</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4565,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465357</v>
+        <v>465321</v>
       </c>
       <c r="R41" t="n">
-        <v>6790909</v>
+        <v>6790871</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4630,7 +4629,7 @@
         <v>131934071</v>
       </c>
       <c r="B42" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4724,37 +4723,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131926775</v>
+        <v>131930537</v>
       </c>
       <c r="B43" t="n">
-        <v>99095</v>
+        <v>57948</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>260</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465321</v>
+        <v>465357</v>
       </c>
       <c r="R43" t="n">
-        <v>6790871</v>
+        <v>6790909</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4828,7 +4828,7 @@
         <v>131933829</v>
       </c>
       <c r="B44" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>131926960</v>
       </c>
       <c r="B45" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5019,49 +5019,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131930390</v>
+        <v>131934704</v>
       </c>
       <c r="B46" t="n">
-        <v>99095</v>
+        <v>79075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465346</v>
+        <v>465369</v>
       </c>
       <c r="R46" t="n">
-        <v>6790951</v>
+        <v>6790822</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5094,11 +5090,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5125,45 +5116,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131934704</v>
+        <v>131930390</v>
       </c>
       <c r="B47" t="n">
-        <v>79073</v>
+        <v>99098</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465369</v>
+        <v>465346</v>
       </c>
       <c r="R47" t="n">
-        <v>6790822</v>
+        <v>6790951</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5196,6 +5191,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5225,7 +5225,7 @@
         <v>131929040</v>
       </c>
       <c r="B48" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>131926542</v>
       </c>
       <c r="B49" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>131930075</v>
       </c>
       <c r="B50" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>131931514</v>
       </c>
       <c r="B51" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>131930457</v>
       </c>
       <c r="B53" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>131934627</v>
       </c>
       <c r="B54" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>131926778</v>
       </c>
       <c r="B55" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>131928437</v>
       </c>
       <c r="B56" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>131927776</v>
       </c>
       <c r="B57" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>131927394</v>
       </c>
       <c r="B59" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>131927401</v>
       </c>
       <c r="B60" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>131928063</v>
       </c>
       <c r="B61" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>131928710</v>
       </c>
       <c r="B62" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>131932080</v>
       </c>
       <c r="B63" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>131926947</v>
       </c>
       <c r="B64" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>131928703</v>
       </c>
       <c r="B65" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131930396</v>
+        <v>131927676</v>
       </c>
       <c r="B67" t="n">
-        <v>79315</v>
+        <v>92352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465346</v>
+        <v>465330</v>
       </c>
       <c r="R67" t="n">
-        <v>6790951</v>
+        <v>6790858</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,32 +7210,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131927676</v>
+        <v>131930396</v>
       </c>
       <c r="B68" t="n">
-        <v>92349</v>
+        <v>79317</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7245,10 +7245,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465330</v>
+        <v>465346</v>
       </c>
       <c r="R68" t="n">
-        <v>6790858</v>
+        <v>6790951</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7412,7 +7412,7 @@
         <v>131931743</v>
       </c>
       <c r="B70" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>131926444</v>
       </c>
       <c r="B71" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>131932356</v>
       </c>
       <c r="B72" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>131926950</v>
       </c>
       <c r="B73" t="n">
-        <v>79905</v>
+        <v>79907</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -4825,45 +4825,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131933829</v>
+        <v>131930390</v>
       </c>
       <c r="B44" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465570</v>
+        <v>465346</v>
       </c>
       <c r="R44" t="n">
-        <v>6790886</v>
+        <v>6790951</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4896,6 +4900,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4922,7 +4931,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131926960</v>
+        <v>131933829</v>
       </c>
       <c r="B45" t="n">
         <v>79317</v>
@@ -4957,13 +4966,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465306</v>
+        <v>465570</v>
       </c>
       <c r="R45" t="n">
-        <v>6790869</v>
+        <v>6790886</v>
       </c>
       <c r="S45" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5019,10 +5028,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934704</v>
+        <v>131926960</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5030,21 +5039,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5054,13 +5063,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465369</v>
+        <v>465306</v>
       </c>
       <c r="R46" t="n">
-        <v>6790822</v>
+        <v>6790869</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5116,49 +5125,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131930390</v>
+        <v>131934704</v>
       </c>
       <c r="B47" t="n">
-        <v>99098</v>
+        <v>79075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465346</v>
+        <v>465369</v>
       </c>
       <c r="R47" t="n">
-        <v>6790951</v>
+        <v>6790822</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5191,11 +5196,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7113,45 +7113,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131927676</v>
+        <v>131931509</v>
       </c>
       <c r="B67" t="n">
-        <v>92352</v>
+        <v>57945</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465330</v>
+        <v>465508</v>
       </c>
       <c r="R67" t="n">
-        <v>6790858</v>
+        <v>6790896</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,32 +7215,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131930396</v>
+        <v>131927676</v>
       </c>
       <c r="B68" t="n">
-        <v>79317</v>
+        <v>92352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7245,10 +7250,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465346</v>
+        <v>465330</v>
       </c>
       <c r="R68" t="n">
-        <v>6790951</v>
+        <v>6790858</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7307,10 +7312,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131931509</v>
+        <v>131930396</v>
       </c>
       <c r="B69" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7318,39 +7323,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465508</v>
+        <v>465346</v>
       </c>
       <c r="R69" t="n">
-        <v>6790896</v>
+        <v>6790951</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7409,10 +7409,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131931743</v>
+        <v>131926950</v>
       </c>
       <c r="B70" t="n">
-        <v>79317</v>
+        <v>79907</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465513</v>
+        <v>465306</v>
       </c>
       <c r="R70" t="n">
-        <v>6790879</v>
+        <v>6790869</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131926444</v>
+        <v>131931743</v>
       </c>
       <c r="B71" t="n">
         <v>79317</v>
@@ -7541,13 +7541,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465326</v>
+        <v>465513</v>
       </c>
       <c r="R71" t="n">
-        <v>6790884</v>
+        <v>6790879</v>
       </c>
       <c r="S71" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7577,11 +7577,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7608,7 +7603,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131932356</v>
+        <v>131926444</v>
       </c>
       <c r="B72" t="n">
         <v>79317</v>
@@ -7643,13 +7638,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465560</v>
+        <v>465326</v>
       </c>
       <c r="R72" t="n">
-        <v>6790913</v>
+        <v>6790884</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7679,6 +7674,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7705,10 +7705,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131926950</v>
+        <v>131932356</v>
       </c>
       <c r="B73" t="n">
-        <v>79907</v>
+        <v>79317</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7716,21 +7716,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7740,13 +7740,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465306</v>
+        <v>465560</v>
       </c>
       <c r="R73" t="n">
-        <v>6790869</v>
+        <v>6790913</v>
       </c>
       <c r="S73" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -7409,10 +7409,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131926950</v>
+        <v>131931743</v>
       </c>
       <c r="B70" t="n">
-        <v>79907</v>
+        <v>79317</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465306</v>
+        <v>465513</v>
       </c>
       <c r="R70" t="n">
-        <v>6790869</v>
+        <v>6790879</v>
       </c>
       <c r="S70" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131931743</v>
+        <v>131926444</v>
       </c>
       <c r="B71" t="n">
         <v>79317</v>
@@ -7541,13 +7541,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465513</v>
+        <v>465326</v>
       </c>
       <c r="R71" t="n">
-        <v>6790879</v>
+        <v>6790884</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7577,6 +7577,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7603,7 +7608,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131926444</v>
+        <v>131932356</v>
       </c>
       <c r="B72" t="n">
         <v>79317</v>
@@ -7638,13 +7643,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465326</v>
+        <v>465560</v>
       </c>
       <c r="R72" t="n">
-        <v>6790884</v>
+        <v>6790913</v>
       </c>
       <c r="S72" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7674,11 +7679,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7705,10 +7705,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131932356</v>
+        <v>131926950</v>
       </c>
       <c r="B73" t="n">
-        <v>79317</v>
+        <v>79907</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7716,21 +7716,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7740,13 +7740,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465560</v>
+        <v>465306</v>
       </c>
       <c r="R73" t="n">
-        <v>6790913</v>
+        <v>6790869</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131933662</v>
+        <v>131933929</v>
       </c>
       <c r="B4" t="n">
-        <v>79317</v>
+        <v>97963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465592</v>
+        <v>465563</v>
       </c>
       <c r="R4" t="n">
-        <v>6790876</v>
+        <v>6790864</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131929045</v>
+        <v>131933662</v>
       </c>
       <c r="B5" t="n">
         <v>79317</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465377</v>
+        <v>465592</v>
       </c>
       <c r="R5" t="n">
-        <v>6790886</v>
+        <v>6790876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131933929</v>
+        <v>131929045</v>
       </c>
       <c r="B6" t="n">
-        <v>97963</v>
+        <v>79317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465563</v>
+        <v>465377</v>
       </c>
       <c r="R6" t="n">
-        <v>6790864</v>
+        <v>6790886</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,48 +1160,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131930461</v>
+        <v>131932655</v>
       </c>
       <c r="B7" t="n">
-        <v>79317</v>
+        <v>57940</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465359</v>
+        <v>465613</v>
       </c>
       <c r="R7" t="n">
-        <v>6790942</v>
+        <v>6790943</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,53 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131932655</v>
+        <v>131930461</v>
       </c>
       <c r="B8" t="n">
-        <v>57940</v>
+        <v>79317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465613</v>
+        <v>465359</v>
       </c>
       <c r="R8" t="n">
-        <v>6790943</v>
+        <v>6790942</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131927769</v>
+        <v>131933121</v>
       </c>
       <c r="B9" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,39 +1370,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465338</v>
+        <v>465608</v>
       </c>
       <c r="R9" t="n">
-        <v>6790853</v>
+        <v>6790896</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131933121</v>
+        <v>131933933</v>
       </c>
       <c r="B10" t="n">
         <v>79317</v>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465608</v>
+        <v>465563</v>
       </c>
       <c r="R10" t="n">
-        <v>6790896</v>
+        <v>6790864</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,7 +1553,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131933933</v>
+        <v>131931121</v>
       </c>
       <c r="B11" t="n">
         <v>79317</v>
@@ -1593,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465563</v>
+        <v>465451</v>
       </c>
       <c r="R11" t="n">
-        <v>6790864</v>
+        <v>6790896</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,6 +1624,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,7 +1655,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131931121</v>
+        <v>131929201</v>
       </c>
       <c r="B12" t="n">
         <v>79317</v>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465451</v>
+        <v>465380</v>
       </c>
       <c r="R12" t="n">
-        <v>6790896</v>
+        <v>6790900</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1726,11 +1726,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,7 +1752,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131929201</v>
+        <v>131928067</v>
       </c>
       <c r="B13" t="n">
         <v>79317</v>
@@ -1792,13 +1787,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465380</v>
+        <v>465342</v>
       </c>
       <c r="R13" t="n">
-        <v>6790900</v>
+        <v>6790879</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1854,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131928067</v>
+        <v>131934127</v>
       </c>
       <c r="B14" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,34 +1860,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465342</v>
+        <v>465537</v>
       </c>
       <c r="R14" t="n">
-        <v>6790879</v>
+        <v>6790847</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131934127</v>
+        <v>131927769</v>
       </c>
       <c r="B15" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,16 +1962,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1982,7 +1982,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1991,13 +1991,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465537</v>
+        <v>465338</v>
       </c>
       <c r="R15" t="n">
-        <v>6790847</v>
+        <v>6790853</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131933367</v>
+        <v>131930082</v>
       </c>
       <c r="B18" t="n">
-        <v>81302</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465599</v>
+        <v>465351</v>
       </c>
       <c r="R18" t="n">
-        <v>6790901</v>
+        <v>6790929</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131930082</v>
+        <v>131933367</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>81302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465351</v>
+        <v>465599</v>
       </c>
       <c r="R19" t="n">
-        <v>6790929</v>
+        <v>6790901</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131928814</v>
+        <v>131933987</v>
       </c>
       <c r="B22" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,34 +2651,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465357</v>
+        <v>465558</v>
       </c>
       <c r="R22" t="n">
-        <v>6790909</v>
+        <v>6790843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131931849</v>
+        <v>131934170</v>
       </c>
       <c r="B23" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,37 +2753,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465512</v>
+        <v>465537</v>
       </c>
       <c r="R23" t="n">
-        <v>6790845</v>
+        <v>6790847</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2834,10 +2844,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131934622</v>
+        <v>131928814</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,21 +2855,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465369</v>
+        <v>465357</v>
       </c>
       <c r="R24" t="n">
-        <v>6790844</v>
+        <v>6790909</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2931,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131933987</v>
+        <v>131931849</v>
       </c>
       <c r="B25" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2942,39 +2952,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465558</v>
+        <v>465512</v>
       </c>
       <c r="R25" t="n">
-        <v>6790843</v>
+        <v>6790845</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131934170</v>
+        <v>131934622</v>
       </c>
       <c r="B26" t="n">
-        <v>57948</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,42 +3049,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465537</v>
+        <v>465369</v>
       </c>
       <c r="R26" t="n">
-        <v>6790847</v>
+        <v>6790844</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,49 +3436,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131931220</v>
+        <v>131933651</v>
       </c>
       <c r="B30" t="n">
-        <v>99098</v>
+        <v>79075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465472</v>
+        <v>465592</v>
       </c>
       <c r="R30" t="n">
-        <v>6790889</v>
+        <v>6790876</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3537,7 +3533,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131929195</v>
+        <v>131931220</v>
       </c>
       <c r="B31" t="n">
         <v>99098</v>
@@ -3567,7 +3563,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>140</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3576,10 +3572,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465380</v>
+        <v>465472</v>
       </c>
       <c r="R31" t="n">
-        <v>6790900</v>
+        <v>6790889</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3612,11 +3608,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3643,7 +3634,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131934382</v>
+        <v>131929195</v>
       </c>
       <c r="B32" t="n">
         <v>99098</v>
@@ -3673,7 +3664,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3682,10 +3673,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465402</v>
+        <v>465380</v>
       </c>
       <c r="R32" t="n">
-        <v>6790848</v>
+        <v>6790900</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3718,6 +3709,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3744,45 +3740,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131933651</v>
+        <v>131934382</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>99098</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465592</v>
+        <v>465402</v>
       </c>
       <c r="R33" t="n">
-        <v>6790876</v>
+        <v>6790848</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3841,10 +3841,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131934634</v>
+        <v>131934641</v>
       </c>
       <c r="B34" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3852,21 +3852,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131934641</v>
+        <v>131934129</v>
       </c>
       <c r="B35" t="n">
         <v>79317</v>
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465369</v>
+        <v>465537</v>
       </c>
       <c r="R35" t="n">
-        <v>6790844</v>
+        <v>6790847</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131934129</v>
+        <v>131933369</v>
       </c>
       <c r="B36" t="n">
         <v>79317</v>
@@ -4070,13 +4070,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465537</v>
+        <v>465599</v>
       </c>
       <c r="R36" t="n">
-        <v>6790847</v>
+        <v>6790901</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131933369</v>
+        <v>131934709</v>
       </c>
       <c r="B37" t="n">
         <v>79317</v>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465599</v>
+        <v>465369</v>
       </c>
       <c r="R37" t="n">
-        <v>6790901</v>
+        <v>6790822</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131934709</v>
+        <v>131934634</v>
       </c>
       <c r="B38" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4240,21 +4240,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4267,7 +4267,7 @@
         <v>465369</v>
       </c>
       <c r="R38" t="n">
-        <v>6790822</v>
+        <v>6790844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4525,49 +4525,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131926775</v>
+        <v>131934071</v>
       </c>
       <c r="B41" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465321</v>
+        <v>465575</v>
       </c>
       <c r="R41" t="n">
-        <v>6790871</v>
+        <v>6790844</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4626,45 +4622,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131934071</v>
+        <v>131926775</v>
       </c>
       <c r="B42" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465575</v>
+        <v>465321</v>
       </c>
       <c r="R42" t="n">
-        <v>6790844</v>
+        <v>6790871</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4825,49 +4825,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131930390</v>
+        <v>131933829</v>
       </c>
       <c r="B44" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465346</v>
+        <v>465570</v>
       </c>
       <c r="R44" t="n">
-        <v>6790951</v>
+        <v>6790886</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4900,11 +4896,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4931,7 +4922,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131933829</v>
+        <v>131926960</v>
       </c>
       <c r="B45" t="n">
         <v>79317</v>
@@ -4966,13 +4957,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465570</v>
+        <v>465306</v>
       </c>
       <c r="R45" t="n">
-        <v>6790886</v>
+        <v>6790869</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5028,10 +5019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131926960</v>
+        <v>131934704</v>
       </c>
       <c r="B46" t="n">
-        <v>79317</v>
+        <v>79075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5039,21 +5030,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5063,13 +5054,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465306</v>
+        <v>465369</v>
       </c>
       <c r="R46" t="n">
-        <v>6790869</v>
+        <v>6790822</v>
       </c>
       <c r="S46" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5125,45 +5116,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131934704</v>
+        <v>131930390</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>99098</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465369</v>
+        <v>465346</v>
       </c>
       <c r="R47" t="n">
-        <v>6790822</v>
+        <v>6790951</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5196,6 +5191,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131929040</v>
+        <v>131931514</v>
       </c>
       <c r="B48" t="n">
-        <v>92352</v>
+        <v>79317</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465377</v>
+        <v>465508</v>
       </c>
       <c r="R48" t="n">
-        <v>6790886</v>
+        <v>6790896</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5319,10 +5319,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131926542</v>
+        <v>131930075</v>
       </c>
       <c r="B49" t="n">
-        <v>92352</v>
+        <v>99098</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5330,37 +5330,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465326</v>
+        <v>465351</v>
       </c>
       <c r="R49" t="n">
-        <v>6790884</v>
+        <v>6790929</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5390,11 +5394,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5421,10 +5420,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131930075</v>
+        <v>131929040</v>
       </c>
       <c r="B50" t="n">
-        <v>99098</v>
+        <v>92352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,38 +5431,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465351</v>
+        <v>465377</v>
       </c>
       <c r="R50" t="n">
-        <v>6790929</v>
+        <v>6790886</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5522,32 +5517,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131931514</v>
+        <v>131926542</v>
       </c>
       <c r="B51" t="n">
-        <v>79317</v>
+        <v>92352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5557,13 +5552,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465508</v>
+        <v>465326</v>
       </c>
       <c r="R51" t="n">
-        <v>6790896</v>
+        <v>6790884</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5593,6 +5588,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5827,10 +5827,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131934627</v>
+        <v>131926778</v>
       </c>
       <c r="B54" t="n">
-        <v>79074</v>
+        <v>79317</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5838,21 +5838,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465369</v>
+        <v>465321</v>
       </c>
       <c r="R54" t="n">
-        <v>6790844</v>
+        <v>6790871</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5924,10 +5924,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131926778</v>
+        <v>131928437</v>
       </c>
       <c r="B55" t="n">
-        <v>79317</v>
+        <v>83297</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5935,21 +5935,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5959,10 +5959,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465321</v>
+        <v>465342</v>
       </c>
       <c r="R55" t="n">
-        <v>6790871</v>
+        <v>6790888</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5995,6 +5995,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6021,10 +6026,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131928437</v>
+        <v>131927776</v>
       </c>
       <c r="B56" t="n">
-        <v>83297</v>
+        <v>79317</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6032,21 +6037,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6061,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465342</v>
+        <v>465338</v>
       </c>
       <c r="R56" t="n">
-        <v>6790888</v>
+        <v>6790853</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6092,11 +6097,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131927776</v>
+        <v>131934627</v>
       </c>
       <c r="B57" t="n">
-        <v>79317</v>
+        <v>79074</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465338</v>
+        <v>465369</v>
       </c>
       <c r="R57" t="n">
-        <v>6790853</v>
+        <v>6790844</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131927394</v>
+        <v>131927401</v>
       </c>
       <c r="B59" t="n">
-        <v>83297</v>
+        <v>79317</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6419,10 +6419,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131927401</v>
+        <v>131927394</v>
       </c>
       <c r="B60" t="n">
-        <v>79317</v>
+        <v>83297</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6430,21 +6430,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131928710</v>
+        <v>131926947</v>
       </c>
       <c r="B62" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,13 +6653,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465359</v>
+        <v>465306</v>
       </c>
       <c r="R62" t="n">
-        <v>6790895</v>
+        <v>6790869</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6689,11 +6689,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6720,10 +6715,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131932080</v>
+        <v>131928703</v>
       </c>
       <c r="B63" t="n">
-        <v>79317</v>
+        <v>79074</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,21 +6726,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6750,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465547</v>
+        <v>465359</v>
       </c>
       <c r="R63" t="n">
-        <v>6790878</v>
+        <v>6790895</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6817,10 +6812,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131926947</v>
+        <v>131932078</v>
       </c>
       <c r="B64" t="n">
-        <v>79936</v>
+        <v>57945</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,37 +6823,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465306</v>
+        <v>465547</v>
       </c>
       <c r="R64" t="n">
-        <v>6790869</v>
+        <v>6790878</v>
       </c>
       <c r="S64" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131928703</v>
+        <v>131928710</v>
       </c>
       <c r="B65" t="n">
-        <v>79074</v>
+        <v>79317</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6985,6 +6985,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7011,10 +7016,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131932078</v>
+        <v>131932080</v>
       </c>
       <c r="B66" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7022,29 +7027,24 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131931509</v>
+        <v>131930396</v>
       </c>
       <c r="B67" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7124,39 +7124,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465508</v>
+        <v>465346</v>
       </c>
       <c r="R67" t="n">
-        <v>6790896</v>
+        <v>6790951</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7312,10 +7307,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131930396</v>
+        <v>131931509</v>
       </c>
       <c r="B69" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7323,34 +7318,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465346</v>
+        <v>465508</v>
       </c>
       <c r="R69" t="n">
-        <v>6790951</v>
+        <v>6790896</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131933367</v>
+        <v>131932725</v>
       </c>
       <c r="B19" t="n">
-        <v>81302</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465599</v>
+        <v>465613</v>
       </c>
       <c r="R19" t="n">
-        <v>6790901</v>
+        <v>6790943</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131932725</v>
+        <v>131933367</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>81302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465613</v>
+        <v>465599</v>
       </c>
       <c r="R20" t="n">
-        <v>6790943</v>
+        <v>6790901</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131928814</v>
+        <v>131934622</v>
       </c>
       <c r="B24" t="n">
-        <v>79317</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2855,21 +2855,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465357</v>
+        <v>465369</v>
       </c>
       <c r="R24" t="n">
-        <v>6790909</v>
+        <v>6790844</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131931849</v>
+        <v>131928814</v>
       </c>
       <c r="B25" t="n">
         <v>79317</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465512</v>
+        <v>465357</v>
       </c>
       <c r="R25" t="n">
-        <v>6790845</v>
+        <v>6790909</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131934622</v>
+        <v>131931849</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465369</v>
+        <v>465512</v>
       </c>
       <c r="R26" t="n">
-        <v>6790844</v>
+        <v>6790845</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -6419,10 +6419,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131927394</v>
+        <v>131928063</v>
       </c>
       <c r="B60" t="n">
-        <v>83297</v>
+        <v>58109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6430,37 +6430,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465330</v>
+        <v>465342</v>
       </c>
       <c r="R60" t="n">
-        <v>6790858</v>
+        <v>6790879</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6516,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131928063</v>
+        <v>131927394</v>
       </c>
       <c r="B61" t="n">
-        <v>58109</v>
+        <v>83297</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6527,42 +6532,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465342</v>
+        <v>465330</v>
       </c>
       <c r="R61" t="n">
-        <v>6790879</v>
+        <v>6790858</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131926947</v>
+        <v>131928710</v>
       </c>
       <c r="B62" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,13 +6653,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465306</v>
+        <v>465359</v>
       </c>
       <c r="R62" t="n">
-        <v>6790869</v>
+        <v>6790895</v>
       </c>
       <c r="S62" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6689,6 +6689,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6715,10 +6720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131928703</v>
+        <v>131932080</v>
       </c>
       <c r="B63" t="n">
-        <v>79074</v>
+        <v>79317</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,21 +6731,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6750,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465359</v>
+        <v>465547</v>
       </c>
       <c r="R63" t="n">
-        <v>6790895</v>
+        <v>6790878</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,10 +6919,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131928710</v>
+        <v>131926947</v>
       </c>
       <c r="B65" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6930,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,13 +6954,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465359</v>
+        <v>465306</v>
       </c>
       <c r="R65" t="n">
-        <v>6790895</v>
+        <v>6790869</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6985,11 +6990,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7016,10 +7016,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131932080</v>
+        <v>131928703</v>
       </c>
       <c r="B66" t="n">
-        <v>79317</v>
+        <v>79074</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465547</v>
+        <v>465359</v>
       </c>
       <c r="R66" t="n">
-        <v>6790878</v>
+        <v>6790895</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131932725</v>
+        <v>131933367</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>81302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465613</v>
+        <v>465599</v>
       </c>
       <c r="R19" t="n">
-        <v>6790943</v>
+        <v>6790901</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131933367</v>
+        <v>131932725</v>
       </c>
       <c r="B20" t="n">
-        <v>81302</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465599</v>
+        <v>465613</v>
       </c>
       <c r="R20" t="n">
-        <v>6790901</v>
+        <v>6790943</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131934622</v>
+        <v>131928814</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2855,21 +2855,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465369</v>
+        <v>465357</v>
       </c>
       <c r="R24" t="n">
-        <v>6790844</v>
+        <v>6790909</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131928814</v>
+        <v>131931849</v>
       </c>
       <c r="B25" t="n">
         <v>79317</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465357</v>
+        <v>465512</v>
       </c>
       <c r="R25" t="n">
-        <v>6790909</v>
+        <v>6790845</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131931849</v>
+        <v>131934622</v>
       </c>
       <c r="B26" t="n">
-        <v>79317</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465512</v>
+        <v>465369</v>
       </c>
       <c r="R26" t="n">
-        <v>6790845</v>
+        <v>6790844</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -6419,10 +6419,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131928063</v>
+        <v>131927394</v>
       </c>
       <c r="B60" t="n">
-        <v>58109</v>
+        <v>83297</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6430,42 +6430,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465342</v>
+        <v>465330</v>
       </c>
       <c r="R60" t="n">
-        <v>6790879</v>
+        <v>6790858</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6521,10 +6516,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131927394</v>
+        <v>131928063</v>
       </c>
       <c r="B61" t="n">
-        <v>83297</v>
+        <v>58109</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,37 +6527,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465330</v>
+        <v>465342</v>
       </c>
       <c r="R61" t="n">
-        <v>6790858</v>
+        <v>6790879</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131928710</v>
+        <v>131926947</v>
       </c>
       <c r="B62" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,13 +6653,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465359</v>
+        <v>465306</v>
       </c>
       <c r="R62" t="n">
-        <v>6790895</v>
+        <v>6790869</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6689,11 +6689,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6720,10 +6715,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131932080</v>
+        <v>131928703</v>
       </c>
       <c r="B63" t="n">
-        <v>79317</v>
+        <v>79074</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,21 +6726,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6750,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465547</v>
+        <v>465359</v>
       </c>
       <c r="R63" t="n">
-        <v>6790878</v>
+        <v>6790895</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6919,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131926947</v>
+        <v>131928710</v>
       </c>
       <c r="B65" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6930,21 +6925,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6954,13 +6949,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465306</v>
+        <v>465359</v>
       </c>
       <c r="R65" t="n">
-        <v>6790869</v>
+        <v>6790895</v>
       </c>
       <c r="S65" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6990,6 +6985,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7016,10 +7016,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131928703</v>
+        <v>131932080</v>
       </c>
       <c r="B66" t="n">
-        <v>79074</v>
+        <v>79317</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465359</v>
+        <v>465547</v>
       </c>
       <c r="R66" t="n">
-        <v>6790895</v>
+        <v>6790878</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -1160,53 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131932655</v>
+        <v>131930461</v>
       </c>
       <c r="B7" t="n">
-        <v>57940</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465613</v>
+        <v>465359</v>
       </c>
       <c r="R7" t="n">
-        <v>6790943</v>
+        <v>6790942</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1262,48 +1257,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131930461</v>
+        <v>131932655</v>
       </c>
       <c r="B8" t="n">
-        <v>79317</v>
+        <v>57940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465359</v>
+        <v>465613</v>
       </c>
       <c r="R8" t="n">
-        <v>6790942</v>
+        <v>6790943</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131933367</v>
+        <v>131932725</v>
       </c>
       <c r="B19" t="n">
-        <v>81302</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465599</v>
+        <v>465613</v>
       </c>
       <c r="R19" t="n">
-        <v>6790901</v>
+        <v>6790943</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131932725</v>
+        <v>131933367</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>81302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465613</v>
+        <v>465599</v>
       </c>
       <c r="R20" t="n">
-        <v>6790943</v>
+        <v>6790901</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131928814</v>
+        <v>131934622</v>
       </c>
       <c r="B24" t="n">
-        <v>79317</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2855,21 +2855,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465357</v>
+        <v>465369</v>
       </c>
       <c r="R24" t="n">
-        <v>6790909</v>
+        <v>6790844</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131931849</v>
+        <v>131928814</v>
       </c>
       <c r="B25" t="n">
         <v>79317</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465512</v>
+        <v>465357</v>
       </c>
       <c r="R25" t="n">
-        <v>6790845</v>
+        <v>6790909</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131934622</v>
+        <v>131931849</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465369</v>
+        <v>465512</v>
       </c>
       <c r="R26" t="n">
-        <v>6790844</v>
+        <v>6790845</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -5319,10 +5319,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131930075</v>
+        <v>131929040</v>
       </c>
       <c r="B49" t="n">
-        <v>99098</v>
+        <v>92352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5330,38 +5330,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465351</v>
+        <v>465377</v>
       </c>
       <c r="R49" t="n">
-        <v>6790929</v>
+        <v>6790886</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5420,7 +5416,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131929040</v>
+        <v>131926542</v>
       </c>
       <c r="B50" t="n">
         <v>92352</v>
@@ -5455,13 +5451,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465377</v>
+        <v>465326</v>
       </c>
       <c r="R50" t="n">
-        <v>6790886</v>
+        <v>6790884</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5491,6 +5487,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5517,10 +5518,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131926542</v>
+        <v>131930075</v>
       </c>
       <c r="B51" t="n">
-        <v>92352</v>
+        <v>99098</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5528,37 +5529,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465326</v>
+        <v>465351</v>
       </c>
       <c r="R51" t="n">
-        <v>6790884</v>
+        <v>6790929</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5588,11 +5593,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131926947</v>
+        <v>131928710</v>
       </c>
       <c r="B62" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,13 +6653,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465306</v>
+        <v>465359</v>
       </c>
       <c r="R62" t="n">
-        <v>6790869</v>
+        <v>6790895</v>
       </c>
       <c r="S62" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6689,6 +6689,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6715,10 +6720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131928703</v>
+        <v>131932080</v>
       </c>
       <c r="B63" t="n">
-        <v>79074</v>
+        <v>79317</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,21 +6731,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6750,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465359</v>
+        <v>465547</v>
       </c>
       <c r="R63" t="n">
-        <v>6790895</v>
+        <v>6790878</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,10 +6919,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131928710</v>
+        <v>131926947</v>
       </c>
       <c r="B65" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6930,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,13 +6954,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465359</v>
+        <v>465306</v>
       </c>
       <c r="R65" t="n">
-        <v>6790895</v>
+        <v>6790869</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6985,11 +6990,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7016,10 +7016,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131932080</v>
+        <v>131928703</v>
       </c>
       <c r="B66" t="n">
-        <v>79317</v>
+        <v>79074</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465547</v>
+        <v>465359</v>
       </c>
       <c r="R66" t="n">
-        <v>6790878</v>
+        <v>6790895</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131930995</v>
       </c>
       <c r="B2" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131933992</v>
       </c>
       <c r="B3" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131933929</v>
       </c>
       <c r="B4" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131933662</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131929045</v>
       </c>
       <c r="B6" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>131930461</v>
       </c>
       <c r="B7" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>131932655</v>
       </c>
       <c r="B8" t="n">
-        <v>57940</v>
+        <v>57941</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>131933121</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131933933</v>
       </c>
       <c r="B10" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>131931121</v>
       </c>
       <c r="B11" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>131929201</v>
       </c>
       <c r="B12" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>131928067</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131934127</v>
+        <v>131927769</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>57949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,16 +1860,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1880,7 +1880,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1889,13 +1889,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465537</v>
+        <v>465338</v>
       </c>
       <c r="R14" t="n">
-        <v>6790847</v>
+        <v>6790853</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131927769</v>
+        <v>131934127</v>
       </c>
       <c r="B15" t="n">
-        <v>57948</v>
+        <v>57946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,16 +1962,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1982,7 +1982,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1991,13 +1991,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465338</v>
+        <v>465537</v>
       </c>
       <c r="R15" t="n">
-        <v>6790853</v>
+        <v>6790847</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131931225</v>
       </c>
       <c r="B16" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>131931931</v>
       </c>
       <c r="B17" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>131930082</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>131932725</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>131933367</v>
       </c>
       <c r="B20" t="n">
-        <v>81302</v>
+        <v>81304</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>131932719</v>
       </c>
       <c r="B21" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131933987</v>
+        <v>131928814</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,39 +2651,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465558</v>
+        <v>465357</v>
       </c>
       <c r="R22" t="n">
-        <v>6790843</v>
+        <v>6790909</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131934170</v>
+        <v>131931849</v>
       </c>
       <c r="B23" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,42 +2748,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465537</v>
+        <v>465512</v>
       </c>
       <c r="R23" t="n">
-        <v>6790847</v>
+        <v>6790845</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2844,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131934622</v>
+        <v>131933987</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>57949</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2855,34 +2845,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465369</v>
+        <v>465558</v>
       </c>
       <c r="R24" t="n">
-        <v>6790844</v>
+        <v>6790843</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2941,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131928814</v>
+        <v>131934170</v>
       </c>
       <c r="B25" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,37 +2947,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465357</v>
+        <v>465537</v>
       </c>
       <c r="R25" t="n">
-        <v>6790909</v>
+        <v>6790847</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131931849</v>
+        <v>131934622</v>
       </c>
       <c r="B26" t="n">
-        <v>79317</v>
+        <v>79077</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465512</v>
+        <v>465369</v>
       </c>
       <c r="R26" t="n">
-        <v>6790845</v>
+        <v>6790844</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131934405</v>
+        <v>131933651</v>
       </c>
       <c r="B27" t="n">
-        <v>79317</v>
+        <v>79077</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,21 +3146,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465402</v>
+        <v>465592</v>
       </c>
       <c r="R27" t="n">
-        <v>6790848</v>
+        <v>6790876</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131930993</v>
+        <v>131934405</v>
       </c>
       <c r="B28" t="n">
-        <v>83297</v>
+        <v>79319</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3243,21 +3243,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465446</v>
+        <v>465402</v>
       </c>
       <c r="R28" t="n">
-        <v>6790876</v>
+        <v>6790848</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3303,11 +3303,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3334,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131928811</v>
+        <v>131930993</v>
       </c>
       <c r="B29" t="n">
-        <v>57945</v>
+        <v>83299</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3345,39 +3340,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465357</v>
+        <v>465446</v>
       </c>
       <c r="R29" t="n">
-        <v>6790909</v>
+        <v>6790876</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3410,6 +3400,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3436,10 +3431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131933651</v>
+        <v>131928811</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>57946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3447,34 +3442,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465592</v>
+        <v>465357</v>
       </c>
       <c r="R30" t="n">
-        <v>6790876</v>
+        <v>6790909</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
         <v>131931220</v>
       </c>
       <c r="B31" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>131929195</v>
       </c>
       <c r="B32" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>131934382</v>
       </c>
       <c r="B33" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131934641</v>
+        <v>131934634</v>
       </c>
       <c r="B34" t="n">
-        <v>79317</v>
+        <v>79938</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3852,21 +3852,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131934129</v>
+        <v>131934641</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465537</v>
+        <v>465369</v>
       </c>
       <c r="R35" t="n">
-        <v>6790847</v>
+        <v>6790844</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131933369</v>
+        <v>131934129</v>
       </c>
       <c r="B36" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4070,13 +4070,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465599</v>
+        <v>465537</v>
       </c>
       <c r="R36" t="n">
-        <v>6790901</v>
+        <v>6790847</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4132,10 +4132,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131934709</v>
+        <v>131933369</v>
       </c>
       <c r="B37" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465369</v>
+        <v>465599</v>
       </c>
       <c r="R37" t="n">
-        <v>6790822</v>
+        <v>6790901</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131934634</v>
+        <v>131934709</v>
       </c>
       <c r="B38" t="n">
-        <v>79936</v>
+        <v>79319</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4240,21 +4240,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4267,7 +4267,7 @@
         <v>465369</v>
       </c>
       <c r="R38" t="n">
-        <v>6790844</v>
+        <v>6790822</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4329,7 +4329,7 @@
         <v>131933749</v>
       </c>
       <c r="B39" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>131933582</v>
       </c>
       <c r="B40" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>131934071</v>
       </c>
       <c r="B41" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4622,37 +4622,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131926775</v>
+        <v>131930537</v>
       </c>
       <c r="B42" t="n">
-        <v>99098</v>
+        <v>57949</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>260</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4661,10 +4662,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465321</v>
+        <v>465357</v>
       </c>
       <c r="R42" t="n">
-        <v>6790871</v>
+        <v>6790909</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,38 +4724,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131930537</v>
+        <v>131926775</v>
       </c>
       <c r="B43" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>260</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465357</v>
+        <v>465321</v>
       </c>
       <c r="R43" t="n">
-        <v>6790909</v>
+        <v>6790871</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4828,7 +4828,7 @@
         <v>131933829</v>
       </c>
       <c r="B44" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>131926960</v>
       </c>
       <c r="B45" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5019,45 +5019,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131934704</v>
+        <v>131930390</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>99106</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465369</v>
+        <v>465346</v>
       </c>
       <c r="R46" t="n">
-        <v>6790822</v>
+        <v>6790951</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5090,6 +5094,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5116,49 +5125,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131930390</v>
+        <v>131934704</v>
       </c>
       <c r="B47" t="n">
-        <v>99098</v>
+        <v>79077</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465346</v>
+        <v>465369</v>
       </c>
       <c r="R47" t="n">
-        <v>6790951</v>
+        <v>6790822</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5191,11 +5196,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5225,7 +5225,7 @@
         <v>131931514</v>
       </c>
       <c r="B48" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>131929040</v>
       </c>
       <c r="B49" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>131926542</v>
       </c>
       <c r="B50" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>131930075</v>
       </c>
       <c r="B51" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>131933577</v>
       </c>
       <c r="B52" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>131930457</v>
       </c>
       <c r="B53" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5827,10 +5827,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131926778</v>
+        <v>131934627</v>
       </c>
       <c r="B54" t="n">
-        <v>79317</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5838,21 +5838,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465321</v>
+        <v>465369</v>
       </c>
       <c r="R54" t="n">
-        <v>6790871</v>
+        <v>6790844</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5924,10 +5924,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131928437</v>
+        <v>131926778</v>
       </c>
       <c r="B55" t="n">
-        <v>83297</v>
+        <v>79319</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5935,21 +5935,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5959,10 +5959,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465342</v>
+        <v>465321</v>
       </c>
       <c r="R55" t="n">
-        <v>6790888</v>
+        <v>6790871</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5995,11 +5995,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6026,10 +6021,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131927776</v>
+        <v>131928437</v>
       </c>
       <c r="B56" t="n">
-        <v>79317</v>
+        <v>83299</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6037,21 +6032,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6061,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465338</v>
+        <v>465342</v>
       </c>
       <c r="R56" t="n">
-        <v>6790853</v>
+        <v>6790888</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6097,6 +6092,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131934627</v>
+        <v>131927776</v>
       </c>
       <c r="B57" t="n">
-        <v>79074</v>
+        <v>79319</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465369</v>
+        <v>465338</v>
       </c>
       <c r="R57" t="n">
-        <v>6790844</v>
+        <v>6790853</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6223,7 +6223,7 @@
         <v>131934550</v>
       </c>
       <c r="B58" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131927401</v>
+        <v>131927394</v>
       </c>
       <c r="B59" t="n">
-        <v>79317</v>
+        <v>83299</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6419,10 +6419,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131927394</v>
+        <v>131927401</v>
       </c>
       <c r="B60" t="n">
-        <v>83297</v>
+        <v>79319</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6430,21 +6430,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6519,7 +6519,7 @@
         <v>131928063</v>
       </c>
       <c r="B61" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131928710</v>
+        <v>131932078</v>
       </c>
       <c r="B62" t="n">
-        <v>79317</v>
+        <v>57946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,34 +6629,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465359</v>
+        <v>465547</v>
       </c>
       <c r="R62" t="n">
-        <v>6790895</v>
+        <v>6790878</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6689,11 +6694,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6720,10 +6720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131932080</v>
+        <v>131928710</v>
       </c>
       <c r="B63" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465547</v>
+        <v>465359</v>
       </c>
       <c r="R63" t="n">
-        <v>6790878</v>
+        <v>6790895</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6791,6 +6791,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6817,10 +6822,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131932078</v>
+        <v>131932080</v>
       </c>
       <c r="B64" t="n">
-        <v>57945</v>
+        <v>79319</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,29 +6833,24 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -6922,7 +6922,7 @@
         <v>131926947</v>
       </c>
       <c r="B65" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>131928703</v>
       </c>
       <c r="B66" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>131930396</v>
       </c>
       <c r="B67" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7210,45 +7210,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131927676</v>
+        <v>131931509</v>
       </c>
       <c r="B68" t="n">
-        <v>92352</v>
+        <v>57946</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465330</v>
+        <v>465508</v>
       </c>
       <c r="R68" t="n">
-        <v>6790858</v>
+        <v>6790896</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7307,50 +7312,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131931509</v>
+        <v>131927676</v>
       </c>
       <c r="B69" t="n">
-        <v>57945</v>
+        <v>92358</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465508</v>
+        <v>465330</v>
       </c>
       <c r="R69" t="n">
-        <v>6790896</v>
+        <v>6790858</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7409,10 +7409,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131931743</v>
+        <v>131926950</v>
       </c>
       <c r="B70" t="n">
-        <v>79317</v>
+        <v>79909</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465513</v>
+        <v>465306</v>
       </c>
       <c r="R70" t="n">
-        <v>6790879</v>
+        <v>6790869</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131926444</v>
+        <v>131931743</v>
       </c>
       <c r="B71" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7541,13 +7541,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465326</v>
+        <v>465513</v>
       </c>
       <c r="R71" t="n">
-        <v>6790884</v>
+        <v>6790879</v>
       </c>
       <c r="S71" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7577,11 +7577,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7608,10 +7603,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131932356</v>
+        <v>131926444</v>
       </c>
       <c r="B72" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7643,13 +7638,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465560</v>
+        <v>465326</v>
       </c>
       <c r="R72" t="n">
-        <v>6790913</v>
+        <v>6790884</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7679,6 +7674,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7705,10 +7705,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131926950</v>
+        <v>131932356</v>
       </c>
       <c r="B73" t="n">
-        <v>79907</v>
+        <v>79319</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7716,21 +7716,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7740,13 +7740,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465306</v>
+        <v>465560</v>
       </c>
       <c r="R73" t="n">
-        <v>6790869</v>
+        <v>6790913</v>
       </c>
       <c r="S73" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>131970205</v>
       </c>
       <c r="B74" t="n">
-        <v>56517</v>
+        <v>56518</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131933929</v>
+        <v>131933662</v>
       </c>
       <c r="B4" t="n">
-        <v>97971</v>
+        <v>79319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465563</v>
+        <v>465592</v>
       </c>
       <c r="R4" t="n">
-        <v>6790864</v>
+        <v>6790876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131933662</v>
+        <v>131929045</v>
       </c>
       <c r="B5" t="n">
         <v>79319</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465592</v>
+        <v>465377</v>
       </c>
       <c r="R5" t="n">
-        <v>6790876</v>
+        <v>6790886</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131929045</v>
+        <v>131933929</v>
       </c>
       <c r="B6" t="n">
-        <v>79319</v>
+        <v>97971</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465377</v>
+        <v>465563</v>
       </c>
       <c r="R6" t="n">
-        <v>6790886</v>
+        <v>6790864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -5319,10 +5319,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131929040</v>
+        <v>131930075</v>
       </c>
       <c r="B49" t="n">
-        <v>92358</v>
+        <v>99106</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5330,34 +5330,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465377</v>
+        <v>465351</v>
       </c>
       <c r="R49" t="n">
-        <v>6790886</v>
+        <v>6790929</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5416,7 +5420,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131926542</v>
+        <v>131929040</v>
       </c>
       <c r="B50" t="n">
         <v>92358</v>
@@ -5451,13 +5455,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465326</v>
+        <v>465377</v>
       </c>
       <c r="R50" t="n">
-        <v>6790884</v>
+        <v>6790886</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5487,11 +5491,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5518,10 +5517,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131930075</v>
+        <v>131926542</v>
       </c>
       <c r="B51" t="n">
-        <v>99106</v>
+        <v>92358</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5529,41 +5528,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465351</v>
+        <v>465326</v>
       </c>
       <c r="R51" t="n">
-        <v>6790929</v>
+        <v>6790884</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5593,6 +5588,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131927394</v>
+        <v>131928063</v>
       </c>
       <c r="B59" t="n">
-        <v>83299</v>
+        <v>58110</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,37 +6333,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465330</v>
+        <v>465342</v>
       </c>
       <c r="R59" t="n">
-        <v>6790858</v>
+        <v>6790879</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6419,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131927401</v>
+        <v>131927394</v>
       </c>
       <c r="B60" t="n">
-        <v>79319</v>
+        <v>83299</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6430,21 +6435,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131928063</v>
+        <v>131927401</v>
       </c>
       <c r="B61" t="n">
-        <v>58110</v>
+        <v>79319</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6527,42 +6532,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465342</v>
+        <v>465330</v>
       </c>
       <c r="R61" t="n">
-        <v>6790879</v>
+        <v>6790858</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131932078</v>
+        <v>131928710</v>
       </c>
       <c r="B62" t="n">
-        <v>57946</v>
+        <v>79319</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,39 +6629,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465547</v>
+        <v>465359</v>
       </c>
       <c r="R62" t="n">
-        <v>6790878</v>
+        <v>6790895</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6694,6 +6689,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6720,7 +6720,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131928710</v>
+        <v>131932080</v>
       </c>
       <c r="B63" t="n">
         <v>79319</v>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465359</v>
+        <v>465547</v>
       </c>
       <c r="R63" t="n">
-        <v>6790895</v>
+        <v>6790878</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6791,11 +6791,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6822,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131932080</v>
+        <v>131926947</v>
       </c>
       <c r="B64" t="n">
-        <v>79319</v>
+        <v>79938</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6833,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6857,13 +6852,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465547</v>
+        <v>465306</v>
       </c>
       <c r="R64" t="n">
-        <v>6790878</v>
+        <v>6790869</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6919,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131926947</v>
+        <v>131928703</v>
       </c>
       <c r="B65" t="n">
-        <v>79938</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6930,21 +6925,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6954,13 +6949,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465306</v>
+        <v>465359</v>
       </c>
       <c r="R65" t="n">
-        <v>6790869</v>
+        <v>6790895</v>
       </c>
       <c r="S65" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7016,10 +7011,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131928703</v>
+        <v>131932078</v>
       </c>
       <c r="B66" t="n">
-        <v>79076</v>
+        <v>57946</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7027,34 +7022,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465359</v>
+        <v>465547</v>
       </c>
       <c r="R66" t="n">
-        <v>6790895</v>
+        <v>6790878</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7409,10 +7409,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131926950</v>
+        <v>131931743</v>
       </c>
       <c r="B70" t="n">
-        <v>79909</v>
+        <v>79319</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465306</v>
+        <v>465513</v>
       </c>
       <c r="R70" t="n">
-        <v>6790869</v>
+        <v>6790879</v>
       </c>
       <c r="S70" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131931743</v>
+        <v>131926444</v>
       </c>
       <c r="B71" t="n">
         <v>79319</v>
@@ -7541,13 +7541,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465513</v>
+        <v>465326</v>
       </c>
       <c r="R71" t="n">
-        <v>6790879</v>
+        <v>6790884</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7577,6 +7577,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7603,7 +7608,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131926444</v>
+        <v>131932356</v>
       </c>
       <c r="B72" t="n">
         <v>79319</v>
@@ -7638,13 +7643,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465326</v>
+        <v>465560</v>
       </c>
       <c r="R72" t="n">
-        <v>6790884</v>
+        <v>6790913</v>
       </c>
       <c r="S72" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7674,11 +7679,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7705,10 +7705,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131932356</v>
+        <v>131926950</v>
       </c>
       <c r="B73" t="n">
-        <v>79319</v>
+        <v>79909</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7716,21 +7716,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7740,13 +7740,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465560</v>
+        <v>465306</v>
       </c>
       <c r="R73" t="n">
-        <v>6790913</v>
+        <v>6790869</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131930995</v>
       </c>
       <c r="B2" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131933992</v>
       </c>
       <c r="B3" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131933662</v>
       </c>
       <c r="B4" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131929045</v>
       </c>
       <c r="B5" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131933929</v>
       </c>
       <c r="B6" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,48 +1160,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131930461</v>
+        <v>131932655</v>
       </c>
       <c r="B7" t="n">
-        <v>79319</v>
+        <v>57945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465359</v>
+        <v>465613</v>
       </c>
       <c r="R7" t="n">
-        <v>6790942</v>
+        <v>6790943</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,53 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131932655</v>
+        <v>131930461</v>
       </c>
       <c r="B8" t="n">
-        <v>57941</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465613</v>
+        <v>465359</v>
       </c>
       <c r="R8" t="n">
-        <v>6790943</v>
+        <v>6790942</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131933121</v>
+        <v>131934127</v>
       </c>
       <c r="B9" t="n">
-        <v>79319</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,37 +1370,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465608</v>
+        <v>465537</v>
       </c>
       <c r="R9" t="n">
-        <v>6790896</v>
+        <v>6790847</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131933933</v>
+        <v>131927769</v>
       </c>
       <c r="B10" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,34 +1472,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465563</v>
+        <v>465338</v>
       </c>
       <c r="R10" t="n">
-        <v>6790864</v>
+        <v>6790853</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131931121</v>
+        <v>131933121</v>
       </c>
       <c r="B11" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,13 +1598,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465451</v>
+        <v>465608</v>
       </c>
       <c r="R11" t="n">
         <v>6790896</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1624,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131929201</v>
+        <v>131933933</v>
       </c>
       <c r="B12" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465380</v>
+        <v>465563</v>
       </c>
       <c r="R12" t="n">
-        <v>6790900</v>
+        <v>6790864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131928067</v>
+        <v>131931121</v>
       </c>
       <c r="B13" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465342</v>
+        <v>465451</v>
       </c>
       <c r="R13" t="n">
-        <v>6790879</v>
+        <v>6790896</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1823,6 +1828,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131927769</v>
+        <v>131929201</v>
       </c>
       <c r="B14" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,39 +1870,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465338</v>
+        <v>465380</v>
       </c>
       <c r="R14" t="n">
-        <v>6790853</v>
+        <v>6790900</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131934127</v>
+        <v>131928067</v>
       </c>
       <c r="B15" t="n">
-        <v>57946</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,39 +1967,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465537</v>
+        <v>465342</v>
       </c>
       <c r="R15" t="n">
-        <v>6790847</v>
+        <v>6790879</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2056,7 +2056,7 @@
         <v>131931225</v>
       </c>
       <c r="B16" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>131931931</v>
       </c>
       <c r="B17" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131930082</v>
+        <v>131933367</v>
       </c>
       <c r="B18" t="n">
-        <v>79319</v>
+        <v>81312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465351</v>
+        <v>465599</v>
       </c>
       <c r="R18" t="n">
-        <v>6790929</v>
+        <v>6790901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131932725</v>
+        <v>131932719</v>
       </c>
       <c r="B19" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,24 +2355,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -2441,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131933367</v>
+        <v>131930082</v>
       </c>
       <c r="B20" t="n">
-        <v>81304</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465599</v>
+        <v>465351</v>
       </c>
       <c r="R20" t="n">
-        <v>6790901</v>
+        <v>6790929</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131932719</v>
+        <v>131932725</v>
       </c>
       <c r="B21" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,29 +2554,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -2643,7 +2643,7 @@
         <v>131928814</v>
       </c>
       <c r="B22" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>131931849</v>
       </c>
       <c r="B23" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>131933987</v>
       </c>
       <c r="B24" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>131934170</v>
       </c>
       <c r="B25" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>131934622</v>
       </c>
       <c r="B26" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,45 +3135,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131933651</v>
+        <v>131931220</v>
       </c>
       <c r="B27" t="n">
-        <v>79077</v>
+        <v>99116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465592</v>
+        <v>465472</v>
       </c>
       <c r="R27" t="n">
-        <v>6790876</v>
+        <v>6790889</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,45 +3236,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131934405</v>
+        <v>131929195</v>
       </c>
       <c r="B28" t="n">
-        <v>79319</v>
+        <v>99116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465402</v>
+        <v>465380</v>
       </c>
       <c r="R28" t="n">
-        <v>6790848</v>
+        <v>6790900</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3303,6 +3311,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,45 +3342,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131930993</v>
+        <v>131934382</v>
       </c>
       <c r="B29" t="n">
-        <v>83299</v>
+        <v>99116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465446</v>
+        <v>465402</v>
       </c>
       <c r="R29" t="n">
-        <v>6790876</v>
+        <v>6790848</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3400,11 +3417,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3431,10 +3443,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131928811</v>
+        <v>131933651</v>
       </c>
       <c r="B30" t="n">
-        <v>57946</v>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,39 +3454,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465357</v>
+        <v>465592</v>
       </c>
       <c r="R30" t="n">
-        <v>6790909</v>
+        <v>6790876</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3533,49 +3540,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131931220</v>
+        <v>131934405</v>
       </c>
       <c r="B31" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465472</v>
+        <v>465402</v>
       </c>
       <c r="R31" t="n">
-        <v>6790889</v>
+        <v>6790848</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3634,49 +3637,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131929195</v>
+        <v>131930993</v>
       </c>
       <c r="B32" t="n">
-        <v>99106</v>
+        <v>83307</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465380</v>
+        <v>465446</v>
       </c>
       <c r="R32" t="n">
-        <v>6790900</v>
+        <v>6790876</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3713,7 +3712,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ca 80 synliga där snön försvunnit</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3740,37 +3739,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131934382</v>
+        <v>131928811</v>
       </c>
       <c r="B33" t="n">
-        <v>99106</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465402</v>
+        <v>465357</v>
       </c>
       <c r="R33" t="n">
-        <v>6790848</v>
+        <v>6790909</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3841,10 +3841,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131934634</v>
+        <v>131934641</v>
       </c>
       <c r="B34" t="n">
-        <v>79938</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3852,21 +3852,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131934641</v>
+        <v>131934129</v>
       </c>
       <c r="B35" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465369</v>
+        <v>465537</v>
       </c>
       <c r="R35" t="n">
-        <v>6790844</v>
+        <v>6790847</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131934129</v>
+        <v>131933749</v>
       </c>
       <c r="B36" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,37 +4046,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465537</v>
+        <v>465570</v>
       </c>
       <c r="R36" t="n">
-        <v>6790847</v>
+        <v>6790886</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4132,10 +4137,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131933369</v>
+        <v>131934634</v>
       </c>
       <c r="B37" t="n">
-        <v>79319</v>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4143,21 +4148,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4172,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465599</v>
+        <v>465369</v>
       </c>
       <c r="R37" t="n">
-        <v>6790901</v>
+        <v>6790844</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4229,10 +4234,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131934709</v>
+        <v>131933369</v>
       </c>
       <c r="B38" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4264,10 +4269,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465369</v>
+        <v>465599</v>
       </c>
       <c r="R38" t="n">
-        <v>6790822</v>
+        <v>6790901</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4326,10 +4331,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131933749</v>
+        <v>131934709</v>
       </c>
       <c r="B39" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4337,39 +4342,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465570</v>
+        <v>465369</v>
       </c>
       <c r="R39" t="n">
-        <v>6790886</v>
+        <v>6790822</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
         <v>131933582</v>
       </c>
       <c r="B40" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131934071</v>
+        <v>131930537</v>
       </c>
       <c r="B41" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4536,34 +4536,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465575</v>
+        <v>465357</v>
       </c>
       <c r="R41" t="n">
-        <v>6790844</v>
+        <v>6790909</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4622,38 +4627,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131930537</v>
+        <v>131926775</v>
       </c>
       <c r="B42" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>260</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4662,10 +4666,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465357</v>
+        <v>465321</v>
       </c>
       <c r="R42" t="n">
-        <v>6790909</v>
+        <v>6790871</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4724,49 +4728,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131926775</v>
+        <v>131934071</v>
       </c>
       <c r="B43" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465321</v>
+        <v>465575</v>
       </c>
       <c r="R43" t="n">
-        <v>6790871</v>
+        <v>6790844</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4825,45 +4825,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131933829</v>
+        <v>131930390</v>
       </c>
       <c r="B44" t="n">
-        <v>79319</v>
+        <v>99116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465570</v>
+        <v>465346</v>
       </c>
       <c r="R44" t="n">
-        <v>6790886</v>
+        <v>6790951</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4896,6 +4900,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4922,10 +4931,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131926960</v>
+        <v>131934704</v>
       </c>
       <c r="B45" t="n">
-        <v>79319</v>
+        <v>79085</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4933,21 +4942,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4957,13 +4966,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465306</v>
+        <v>465369</v>
       </c>
       <c r="R45" t="n">
-        <v>6790869</v>
+        <v>6790822</v>
       </c>
       <c r="S45" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5019,49 +5028,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131930390</v>
+        <v>131933829</v>
       </c>
       <c r="B46" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465346</v>
+        <v>465570</v>
       </c>
       <c r="R46" t="n">
-        <v>6790951</v>
+        <v>6790886</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5094,11 +5099,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5125,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131934704</v>
+        <v>131926960</v>
       </c>
       <c r="B47" t="n">
-        <v>79077</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,13 +5160,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465369</v>
+        <v>465306</v>
       </c>
       <c r="R47" t="n">
-        <v>6790822</v>
+        <v>6790869</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131931514</v>
+        <v>131929040</v>
       </c>
       <c r="B48" t="n">
-        <v>79319</v>
+        <v>92368</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465508</v>
+        <v>465377</v>
       </c>
       <c r="R48" t="n">
-        <v>6790896</v>
+        <v>6790886</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5319,10 +5319,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131930075</v>
+        <v>131926542</v>
       </c>
       <c r="B49" t="n">
-        <v>99106</v>
+        <v>92368</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5330,41 +5330,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465351</v>
+        <v>465326</v>
       </c>
       <c r="R49" t="n">
-        <v>6790929</v>
+        <v>6790884</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5394,6 +5390,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5420,32 +5421,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131929040</v>
+        <v>131931514</v>
       </c>
       <c r="B50" t="n">
-        <v>92358</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5455,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465377</v>
+        <v>465508</v>
       </c>
       <c r="R50" t="n">
-        <v>6790886</v>
+        <v>6790896</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5517,10 +5518,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131926542</v>
+        <v>131930075</v>
       </c>
       <c r="B51" t="n">
-        <v>92358</v>
+        <v>99116</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5528,37 +5529,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465326</v>
+        <v>465351</v>
       </c>
       <c r="R51" t="n">
-        <v>6790884</v>
+        <v>6790929</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5588,11 +5593,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5622,7 +5622,7 @@
         <v>131933577</v>
       </c>
       <c r="B52" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>131930457</v>
       </c>
       <c r="B53" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>131934627</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>131926778</v>
       </c>
       <c r="B55" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>131928437</v>
       </c>
       <c r="B56" t="n">
-        <v>83299</v>
+        <v>83307</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>131927776</v>
       </c>
       <c r="B57" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>131934550</v>
       </c>
       <c r="B58" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>131928063</v>
       </c>
       <c r="B59" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>131927394</v>
       </c>
       <c r="B60" t="n">
-        <v>83299</v>
+        <v>83307</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>131927401</v>
       </c>
       <c r="B61" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>131928710</v>
       </c>
       <c r="B62" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>131932080</v>
       </c>
       <c r="B63" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>131926947</v>
       </c>
       <c r="B64" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>131928703</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>131932078</v>
       </c>
       <c r="B66" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131930396</v>
+        <v>131927676</v>
       </c>
       <c r="B67" t="n">
-        <v>79319</v>
+        <v>92368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465346</v>
+        <v>465330</v>
       </c>
       <c r="R67" t="n">
-        <v>6790951</v>
+        <v>6790858</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,10 +7210,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131931509</v>
+        <v>131930396</v>
       </c>
       <c r="B68" t="n">
-        <v>57946</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7221,39 +7221,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465508</v>
+        <v>465346</v>
       </c>
       <c r="R68" t="n">
-        <v>6790896</v>
+        <v>6790951</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7312,45 +7307,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131927676</v>
+        <v>131931509</v>
       </c>
       <c r="B69" t="n">
-        <v>92358</v>
+        <v>57950</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465330</v>
+        <v>465508</v>
       </c>
       <c r="R69" t="n">
-        <v>6790858</v>
+        <v>6790896</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7412,7 +7412,7 @@
         <v>131931743</v>
       </c>
       <c r="B70" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>131926444</v>
       </c>
       <c r="B71" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>131932356</v>
       </c>
       <c r="B72" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>131926950</v>
       </c>
       <c r="B73" t="n">
-        <v>79909</v>
+        <v>79917</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>131970205</v>
       </c>
       <c r="B74" t="n">
-        <v>56518</v>
+        <v>56522</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131931849</v>
+        <v>131934622</v>
       </c>
       <c r="B23" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465512</v>
+        <v>465369</v>
       </c>
       <c r="R23" t="n">
-        <v>6790845</v>
+        <v>6790844</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131933987</v>
+        <v>131931849</v>
       </c>
       <c r="B24" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,39 +2845,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465558</v>
+        <v>465512</v>
       </c>
       <c r="R24" t="n">
-        <v>6790843</v>
+        <v>6790845</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,7 +2931,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131934170</v>
+        <v>131933987</v>
       </c>
       <c r="B25" t="n">
         <v>57953</v>
@@ -2976,13 +2971,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465537</v>
+        <v>465558</v>
       </c>
       <c r="R25" t="n">
-        <v>6790847</v>
+        <v>6790843</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3038,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131934622</v>
+        <v>131934170</v>
       </c>
       <c r="B26" t="n">
-        <v>79085</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3049,37 +3044,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465369</v>
+        <v>465537</v>
       </c>
       <c r="R26" t="n">
-        <v>6790844</v>
+        <v>6790847</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4825,49 +4825,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131930390</v>
+        <v>131933829</v>
       </c>
       <c r="B44" t="n">
-        <v>99116</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465346</v>
+        <v>465570</v>
       </c>
       <c r="R44" t="n">
-        <v>6790951</v>
+        <v>6790886</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4900,11 +4896,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4931,10 +4922,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131934704</v>
+        <v>131926960</v>
       </c>
       <c r="B45" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4942,21 +4933,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4966,13 +4957,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465369</v>
+        <v>465306</v>
       </c>
       <c r="R45" t="n">
-        <v>6790822</v>
+        <v>6790869</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5028,45 +5019,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131933829</v>
+        <v>131930390</v>
       </c>
       <c r="B46" t="n">
-        <v>79327</v>
+        <v>99116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465570</v>
+        <v>465346</v>
       </c>
       <c r="R46" t="n">
-        <v>6790886</v>
+        <v>6790951</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5099,6 +5094,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en större yta, 500 eller fler!</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5125,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131926960</v>
+        <v>131934704</v>
       </c>
       <c r="B47" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,13 +5160,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465306</v>
+        <v>465369</v>
       </c>
       <c r="R47" t="n">
-        <v>6790869</v>
+        <v>6790822</v>
       </c>
       <c r="S47" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5827,10 +5827,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131934627</v>
+        <v>131934550</v>
       </c>
       <c r="B54" t="n">
-        <v>79084</v>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5838,24 +5838,29 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -5924,10 +5929,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131926778</v>
+        <v>131934627</v>
       </c>
       <c r="B55" t="n">
-        <v>79327</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5935,21 +5940,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5959,10 +5964,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465321</v>
+        <v>465369</v>
       </c>
       <c r="R55" t="n">
-        <v>6790871</v>
+        <v>6790844</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6021,10 +6026,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131928437</v>
+        <v>131926778</v>
       </c>
       <c r="B56" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6032,21 +6037,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6061,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465342</v>
+        <v>465321</v>
       </c>
       <c r="R56" t="n">
-        <v>6790888</v>
+        <v>6790871</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6092,11 +6097,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131927776</v>
+        <v>131928437</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>83307</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465338</v>
+        <v>465342</v>
       </c>
       <c r="R57" t="n">
-        <v>6790853</v>
+        <v>6790888</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,6 +6194,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6220,10 +6225,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131934550</v>
+        <v>131927776</v>
       </c>
       <c r="B58" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6231,39 +6236,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465369</v>
+        <v>465338</v>
       </c>
       <c r="R58" t="n">
-        <v>6790844</v>
+        <v>6790853</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131927676</v>
+        <v>131930396</v>
       </c>
       <c r="B67" t="n">
-        <v>92368</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465330</v>
+        <v>465346</v>
       </c>
       <c r="R67" t="n">
-        <v>6790858</v>
+        <v>6790951</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,10 +7210,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131930396</v>
+        <v>131931509</v>
       </c>
       <c r="B68" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7221,34 +7221,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465346</v>
+        <v>465508</v>
       </c>
       <c r="R68" t="n">
-        <v>6790951</v>
+        <v>6790896</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7307,50 +7312,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131931509</v>
+        <v>131927676</v>
       </c>
       <c r="B69" t="n">
-        <v>57950</v>
+        <v>92368</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465508</v>
+        <v>465330</v>
       </c>
       <c r="R69" t="n">
-        <v>6790896</v>
+        <v>6790858</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131930995</v>
+        <v>131933367</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>81355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465446</v>
+        <v>465599</v>
       </c>
       <c r="R2" t="n">
-        <v>6790876</v>
+        <v>6790901</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131933992</v>
+        <v>131926542</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465558</v>
+        <v>465326</v>
       </c>
       <c r="R3" t="n">
-        <v>6790843</v>
+        <v>6790884</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131933662</v>
+        <v>131927676</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>92406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465592</v>
+        <v>465330</v>
       </c>
       <c r="R4" t="n">
-        <v>6790876</v>
+        <v>6790858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131929045</v>
+        <v>131929040</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>92406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131933929</v>
+        <v>131931926</v>
       </c>
       <c r="B6" t="n">
-        <v>97981</v>
+        <v>92188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>3008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465563</v>
+        <v>465523</v>
       </c>
       <c r="R6" t="n">
-        <v>6790864</v>
+        <v>6790868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,53 +1165,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131932655</v>
+        <v>131926062</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465613</v>
+        <v>465306</v>
       </c>
       <c r="R7" t="n">
-        <v>6790943</v>
+        <v>6790869</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 40 meter, synfältet</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,14 +1267,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131930461</v>
+        <v>131926444</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1297,13 +1302,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465359</v>
+        <v>465326</v>
       </c>
       <c r="R8" t="n">
-        <v>6790942</v>
+        <v>6790884</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1333,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,53 +1369,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131934127</v>
+        <v>131926778</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465537</v>
+        <v>465321</v>
       </c>
       <c r="R9" t="n">
-        <v>6790847</v>
+        <v>6790871</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1461,50 +1466,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131927769</v>
+        <v>131927253</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465338</v>
+        <v>465330</v>
       </c>
       <c r="R10" t="n">
-        <v>6790853</v>
+        <v>6790858</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1537,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt i omgivningen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,14 +1568,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131933121</v>
+        <v>131927776</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1598,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465608</v>
+        <v>465338</v>
       </c>
       <c r="R11" t="n">
-        <v>6790896</v>
+        <v>6790853</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,14 +1665,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131933933</v>
+        <v>131928067</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1695,13 +1700,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465563</v>
+        <v>465342</v>
       </c>
       <c r="R12" t="n">
-        <v>6790864</v>
+        <v>6790879</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1757,14 +1762,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131931121</v>
+        <v>131928710</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1792,13 +1797,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465451</v>
+        <v>465359</v>
       </c>
       <c r="R13" t="n">
-        <v>6790896</v>
+        <v>6790895</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1832,7 +1837,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,14 +1864,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131929201</v>
+        <v>131928814</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1894,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465380</v>
+        <v>465357</v>
       </c>
       <c r="R14" t="n">
-        <v>6790900</v>
+        <v>6790909</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,14 +1961,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131928067</v>
+        <v>131929045</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1991,13 +1996,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465342</v>
+        <v>465377</v>
       </c>
       <c r="R15" t="n">
-        <v>6790879</v>
+        <v>6790886</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2053,14 +2058,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131931225</v>
+        <v>131929201</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465472</v>
+        <v>465380</v>
       </c>
       <c r="R16" t="n">
-        <v>6790889</v>
+        <v>6790900</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,14 +2155,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131931931</v>
+        <v>131929917</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2185,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465523</v>
+        <v>465351</v>
       </c>
       <c r="R17" t="n">
-        <v>6790868</v>
+        <v>6790929</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,32 +2252,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131933367</v>
+        <v>131930188</v>
       </c>
       <c r="B18" t="n">
-        <v>81312</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465599</v>
+        <v>465337</v>
       </c>
       <c r="R18" t="n">
-        <v>6790901</v>
+        <v>6790965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,53 +2349,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131932719</v>
+        <v>131930396</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465613</v>
+        <v>465346</v>
       </c>
       <c r="R19" t="n">
-        <v>6790943</v>
+        <v>6790951</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2446,14 +2446,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131930082</v>
+        <v>131930461</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465351</v>
+        <v>465359</v>
       </c>
       <c r="R20" t="n">
-        <v>6790929</v>
+        <v>6790942</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2543,14 +2543,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131932725</v>
+        <v>131930995</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465613</v>
+        <v>465446</v>
       </c>
       <c r="R21" t="n">
-        <v>6790943</v>
+        <v>6790876</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2640,14 +2640,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131928814</v>
+        <v>131931121</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465357</v>
+        <v>465451</v>
       </c>
       <c r="R22" t="n">
-        <v>6790909</v>
+        <v>6790896</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2711,6 +2711,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2737,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131934622</v>
+        <v>131931225</v>
       </c>
       <c r="B23" t="n">
-        <v>79085</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465369</v>
+        <v>465472</v>
       </c>
       <c r="R23" t="n">
-        <v>6790844</v>
+        <v>6790889</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,14 +2839,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131931849</v>
+        <v>131931514</v>
       </c>
       <c r="B24" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2869,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465512</v>
+        <v>465508</v>
       </c>
       <c r="R24" t="n">
-        <v>6790845</v>
+        <v>6790896</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2931,50 +2936,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131933987</v>
+        <v>131931575</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465558</v>
+        <v>465512</v>
       </c>
       <c r="R25" t="n">
-        <v>6790843</v>
+        <v>6790914</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,53 +3033,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131934170</v>
+        <v>131931743</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465537</v>
+        <v>465513</v>
       </c>
       <c r="R26" t="n">
-        <v>6790847</v>
+        <v>6790879</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3135,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131931220</v>
+        <v>131931849</v>
       </c>
       <c r="B27" t="n">
-        <v>99116</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,38 +3141,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465472</v>
+        <v>465512</v>
       </c>
       <c r="R27" t="n">
-        <v>6790889</v>
+        <v>6790845</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3236,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131929195</v>
+        <v>131931931</v>
       </c>
       <c r="B28" t="n">
-        <v>99116</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3247,38 +3238,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465380</v>
+        <v>465523</v>
       </c>
       <c r="R28" t="n">
-        <v>6790900</v>
+        <v>6790868</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3342,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131934382</v>
+        <v>131932080</v>
       </c>
       <c r="B29" t="n">
-        <v>99116</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3353,38 +3335,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465402</v>
+        <v>465547</v>
       </c>
       <c r="R29" t="n">
-        <v>6790848</v>
+        <v>6790878</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3443,32 +3421,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131933651</v>
+        <v>131932356</v>
       </c>
       <c r="B30" t="n">
-        <v>79085</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3478,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465592</v>
+        <v>465560</v>
       </c>
       <c r="R30" t="n">
-        <v>6790876</v>
+        <v>6790913</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3540,14 +3518,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131934405</v>
+        <v>131932660</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3575,13 +3553,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465402</v>
+        <v>465613</v>
       </c>
       <c r="R31" t="n">
-        <v>6790848</v>
+        <v>6790943</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3637,32 +3615,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131930993</v>
+        <v>131933121</v>
       </c>
       <c r="B32" t="n">
-        <v>83307</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3672,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465446</v>
+        <v>465608</v>
       </c>
       <c r="R32" t="n">
-        <v>6790876</v>
+        <v>6790896</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3708,11 +3686,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3739,50 +3712,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131928811</v>
+        <v>131933369</v>
       </c>
       <c r="B33" t="n">
-        <v>57950</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465357</v>
+        <v>465599</v>
       </c>
       <c r="R33" t="n">
-        <v>6790909</v>
+        <v>6790901</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3841,14 +3809,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131934641</v>
+        <v>131933582</v>
       </c>
       <c r="B34" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3876,10 +3844,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465369</v>
+        <v>465598</v>
       </c>
       <c r="R34" t="n">
-        <v>6790844</v>
+        <v>6790885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3938,14 +3906,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131934129</v>
+        <v>131933662</v>
       </c>
       <c r="B35" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3973,13 +3941,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465537</v>
+        <v>465592</v>
       </c>
       <c r="R35" t="n">
-        <v>6790847</v>
+        <v>6790876</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4035,40 +4003,35 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131933749</v>
+        <v>131933756</v>
       </c>
       <c r="B36" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -4137,32 +4100,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131934634</v>
+        <v>131933933</v>
       </c>
       <c r="B37" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4172,10 +4135,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465369</v>
+        <v>465563</v>
       </c>
       <c r="R37" t="n">
-        <v>6790844</v>
+        <v>6790864</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4234,14 +4197,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131933369</v>
+        <v>131933992</v>
       </c>
       <c r="B38" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4269,10 +4232,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465599</v>
+        <v>465558</v>
       </c>
       <c r="R38" t="n">
-        <v>6790901</v>
+        <v>6790843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4331,14 +4294,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131934709</v>
+        <v>131934071</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4366,10 +4329,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465369</v>
+        <v>465575</v>
       </c>
       <c r="R39" t="n">
-        <v>6790822</v>
+        <v>6790844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4428,14 +4391,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131933582</v>
+        <v>131934129</v>
       </c>
       <c r="B40" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4463,13 +4426,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465598</v>
+        <v>465537</v>
       </c>
       <c r="R40" t="n">
-        <v>6790885</v>
+        <v>6790847</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4525,50 +4488,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131930537</v>
+        <v>131934386</v>
       </c>
       <c r="B41" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465357</v>
+        <v>465402</v>
       </c>
       <c r="R41" t="n">
-        <v>6790909</v>
+        <v>6790848</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4627,10 +4585,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131926775</v>
+        <v>131934557</v>
       </c>
       <c r="B42" t="n">
-        <v>99116</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4638,38 +4596,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465321</v>
+        <v>465369</v>
       </c>
       <c r="R42" t="n">
-        <v>6790871</v>
+        <v>6790844</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4728,14 +4682,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131934071</v>
+        <v>131934709</v>
       </c>
       <c r="B43" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4763,10 +4717,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465575</v>
+        <v>465369</v>
       </c>
       <c r="R43" t="n">
-        <v>6790844</v>
+        <v>6790822</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4825,10 +4779,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131933829</v>
+        <v>131927394</v>
       </c>
       <c r="B44" t="n">
-        <v>79327</v>
+        <v>83358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4836,21 +4790,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4860,10 +4814,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465570</v>
+        <v>465330</v>
       </c>
       <c r="R44" t="n">
-        <v>6790886</v>
+        <v>6790858</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4922,10 +4876,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131926960</v>
+        <v>131928437</v>
       </c>
       <c r="B45" t="n">
-        <v>79327</v>
+        <v>83358</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4933,21 +4887,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4957,13 +4911,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465306</v>
+        <v>465342</v>
       </c>
       <c r="R45" t="n">
-        <v>6790869</v>
+        <v>6790888</v>
       </c>
       <c r="S45" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4993,6 +4947,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5019,49 +4978,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131930390</v>
+        <v>131930993</v>
       </c>
       <c r="B46" t="n">
-        <v>99116</v>
+        <v>83358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465346</v>
+        <v>465446</v>
       </c>
       <c r="R46" t="n">
-        <v>6790951</v>
+        <v>6790876</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5098,7 +5053,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På en större yta, 500 eller fler!</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5125,10 +5080,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131934704</v>
+        <v>131928703</v>
       </c>
       <c r="B47" t="n">
-        <v>79085</v>
+        <v>79130</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5091,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,10 +5115,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465369</v>
+        <v>465359</v>
       </c>
       <c r="R47" t="n">
-        <v>6790822</v>
+        <v>6790895</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5222,32 +5177,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131929040</v>
+        <v>131934627</v>
       </c>
       <c r="B48" t="n">
-        <v>92368</v>
+        <v>79130</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5212,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465377</v>
+        <v>465369</v>
       </c>
       <c r="R48" t="n">
-        <v>6790886</v>
+        <v>6790844</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5319,32 +5274,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131926542</v>
+        <v>131926947</v>
       </c>
       <c r="B49" t="n">
-        <v>92368</v>
+        <v>79992</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5354,13 +5309,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465326</v>
+        <v>465306</v>
       </c>
       <c r="R49" t="n">
-        <v>6790884</v>
+        <v>6790869</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5390,11 +5345,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Fler vedsvampar på samma låga</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5421,10 +5371,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131931514</v>
+        <v>131934634</v>
       </c>
       <c r="B50" t="n">
-        <v>79327</v>
+        <v>79992</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,21 +5382,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5456,10 +5406,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465508</v>
+        <v>465369</v>
       </c>
       <c r="R50" t="n">
-        <v>6790896</v>
+        <v>6790844</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5518,37 +5468,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131930075</v>
+        <v>131928811</v>
       </c>
       <c r="B51" t="n">
-        <v>99116</v>
+        <v>57972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5557,10 +5508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465351</v>
+        <v>465357</v>
       </c>
       <c r="R51" t="n">
-        <v>6790929</v>
+        <v>6790909</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5619,27 +5570,27 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131933577</v>
+        <v>131931509</v>
       </c>
       <c r="B52" t="n">
-        <v>57953</v>
+        <v>57972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5650,7 +5601,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5659,10 +5610,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465598</v>
+        <v>465508</v>
       </c>
       <c r="R52" t="n">
-        <v>6790885</v>
+        <v>6790896</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5721,37 +5672,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131930457</v>
+        <v>131932078</v>
       </c>
       <c r="B53" t="n">
-        <v>99116</v>
+        <v>57972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5760,10 +5712,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465359</v>
+        <v>465547</v>
       </c>
       <c r="R53" t="n">
-        <v>6790942</v>
+        <v>6790878</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5796,11 +5748,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Många dolda under snön</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5827,14 +5774,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131934550</v>
+        <v>131934127</v>
       </c>
       <c r="B54" t="n">
-        <v>57950</v>
+        <v>57972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -5858,7 +5805,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5867,13 +5814,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465369</v>
+        <v>465537</v>
       </c>
       <c r="R54" t="n">
-        <v>6790844</v>
+        <v>6790847</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5929,35 +5876,40 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131934627</v>
+        <v>131934550</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>57972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
@@ -6026,10 +5978,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131926778</v>
+        <v>131927769</v>
       </c>
       <c r="B56" t="n">
-        <v>79327</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6037,34 +5989,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465321</v>
+        <v>465338</v>
       </c>
       <c r="R56" t="n">
-        <v>6790871</v>
+        <v>6790853</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6123,10 +6080,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131928437</v>
+        <v>131930537</v>
       </c>
       <c r="B57" t="n">
-        <v>83307</v>
+        <v>57975</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,34 +6091,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465342</v>
+        <v>465357</v>
       </c>
       <c r="R57" t="n">
-        <v>6790888</v>
+        <v>6790909</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,11 +6156,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6225,10 +6182,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131927776</v>
+        <v>131931571</v>
       </c>
       <c r="B58" t="n">
-        <v>79327</v>
+        <v>57975</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6236,34 +6193,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465338</v>
+        <v>465512</v>
       </c>
       <c r="R58" t="n">
-        <v>6790853</v>
+        <v>6790914</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6322,10 +6284,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131928063</v>
+        <v>131932719</v>
       </c>
       <c r="B59" t="n">
-        <v>58114</v>
+        <v>57975</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,27 +6295,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6362,10 +6324,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465342</v>
+        <v>465613</v>
       </c>
       <c r="R59" t="n">
-        <v>6790879</v>
+        <v>6790943</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6424,10 +6386,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131927394</v>
+        <v>131933577</v>
       </c>
       <c r="B60" t="n">
-        <v>83307</v>
+        <v>57975</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6435,34 +6397,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465330</v>
+        <v>465598</v>
       </c>
       <c r="R60" t="n">
-        <v>6790858</v>
+        <v>6790885</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6521,10 +6488,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131927401</v>
+        <v>131933749</v>
       </c>
       <c r="B61" t="n">
-        <v>79327</v>
+        <v>57975</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,34 +6499,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465330</v>
+        <v>465570</v>
       </c>
       <c r="R61" t="n">
-        <v>6790858</v>
+        <v>6790886</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6618,10 +6590,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131928710</v>
+        <v>131933987</v>
       </c>
       <c r="B62" t="n">
-        <v>79327</v>
+        <v>57975</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,34 +6601,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465359</v>
+        <v>465558</v>
       </c>
       <c r="R62" t="n">
-        <v>6790895</v>
+        <v>6790843</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6689,11 +6666,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6720,10 +6692,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131932080</v>
+        <v>131934170</v>
       </c>
       <c r="B63" t="n">
-        <v>79327</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,37 +6703,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465547</v>
+        <v>465537</v>
       </c>
       <c r="R63" t="n">
-        <v>6790878</v>
+        <v>6790847</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6817,48 +6794,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131926947</v>
+        <v>131932655</v>
       </c>
       <c r="B64" t="n">
-        <v>79946</v>
+        <v>57967</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>100110</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465306</v>
+        <v>465613</v>
       </c>
       <c r="R64" t="n">
-        <v>6790869</v>
+        <v>6790943</v>
       </c>
       <c r="S64" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6914,10 +6896,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131928703</v>
+        <v>131928063</v>
       </c>
       <c r="B65" t="n">
-        <v>79084</v>
+        <v>58136</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,37 +6907,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465359</v>
+        <v>465342</v>
       </c>
       <c r="R65" t="n">
-        <v>6790895</v>
+        <v>6790879</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7011,27 +6998,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131932078</v>
+        <v>131932657</v>
       </c>
       <c r="B66" t="n">
-        <v>57950</v>
+        <v>58131</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>103023</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7042,7 +7029,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7051,13 +7038,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465547</v>
+        <v>465613</v>
       </c>
       <c r="R66" t="n">
-        <v>6790878</v>
+        <v>6790943</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7113,10 +7100,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131930396</v>
+        <v>131970205</v>
       </c>
       <c r="B67" t="n">
-        <v>79327</v>
+        <v>56539</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7124,34 +7111,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465346</v>
+        <v>465360</v>
       </c>
       <c r="R67" t="n">
-        <v>6790951</v>
+        <v>6790880</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,10 +7205,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131931509</v>
+        <v>131933399</v>
       </c>
       <c r="B68" t="n">
-        <v>57950</v>
+        <v>56706</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7221,16 +7216,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>206046</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7241,7 +7236,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7250,10 +7245,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465508</v>
+        <v>465599</v>
       </c>
       <c r="R68" t="n">
-        <v>6790896</v>
+        <v>6790901</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7312,45 +7307,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131927676</v>
+        <v>131970210</v>
       </c>
       <c r="B69" t="n">
-        <v>92368</v>
+        <v>56706</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>206046</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465330</v>
+        <v>465372</v>
       </c>
       <c r="R69" t="n">
-        <v>6790858</v>
+        <v>6790873</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7409,45 +7412,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131931743</v>
+        <v>131926672</v>
       </c>
       <c r="B70" t="n">
-        <v>79327</v>
+        <v>99195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465513</v>
+        <v>465321</v>
       </c>
       <c r="R70" t="n">
-        <v>6790879</v>
+        <v>6790871</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7506,48 +7513,52 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131926444</v>
+        <v>131929195</v>
       </c>
       <c r="B71" t="n">
-        <v>79327</v>
+        <v>99195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465326</v>
+        <v>465380</v>
       </c>
       <c r="R71" t="n">
-        <v>6790884</v>
+        <v>6790900</v>
       </c>
       <c r="S71" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7581,7 +7592,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>Ca 80 synliga där snön försvunnit</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7608,45 +7619,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131932356</v>
+        <v>131929915</v>
       </c>
       <c r="B72" t="n">
-        <v>79327</v>
+        <v>99195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465560</v>
+        <v>465351</v>
       </c>
       <c r="R72" t="n">
-        <v>6790913</v>
+        <v>6790929</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7705,48 +7720,52 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131926950</v>
+        <v>131930182</v>
       </c>
       <c r="B73" t="n">
-        <v>79917</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465306</v>
+        <v>465337</v>
       </c>
       <c r="R73" t="n">
-        <v>6790869</v>
+        <v>6790965</v>
       </c>
       <c r="S73" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7776,6 +7795,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Nära hyggeskant</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7802,53 +7826,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131970205</v>
+        <v>131930390</v>
       </c>
       <c r="B74" t="n">
-        <v>56522</v>
+        <v>99195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långfallsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465360</v>
+        <v>465346</v>
       </c>
       <c r="R74" t="n">
-        <v>6790880</v>
+        <v>6790951</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7883,6 +7903,11 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På en större yta, 500 eller fler!</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -7904,6 +7929,904 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131930457</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Långfallsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>465359</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6790942</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Många dolda under snön</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131931220</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Långfallsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>465472</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6790889</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131934382</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Långfallsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>465402</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6790848</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>131933929</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Långfallsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>465563</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6790864</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>67164036</v>
+      </c>
+      <c r="B79" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>S Blecksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>465373</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6790785</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Intill stort hygge. Bakom stor asp, synlig från vägen över hygget, finns liggande granvälta. Vattenhål intill. Flera trolldruveplantor.</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>131933651</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Långfallsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>465592</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6790876</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>131934622</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Långfallsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>465369</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6790844</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>131934704</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Långfallsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>465369</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6790822</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>131926950</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Långfallsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>465306</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6790869</v>
+      </c>
+      <c r="S83" t="n">
+        <v>40</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AZ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933367</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926542</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131927676</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131929040</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964386</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931926</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926062</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926444</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926778</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131927253</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131927776</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928067</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928710</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928814</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131929045</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131929201</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131929917</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930188</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930396</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930461</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2734,6 +2839,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930995</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2836,6 +2946,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931121</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2933,6 +3048,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931225</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3030,6 +3150,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931514</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3127,6 +3252,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931575</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3224,6 +3354,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931743</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3321,6 +3456,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931849</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3418,6 +3558,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931931</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3515,6 +3660,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932080</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3612,6 +3762,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932356</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3709,6 +3864,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932660</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3806,6 +3966,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933121</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3903,6 +4068,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933369</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4000,6 +4170,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933582</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4097,6 +4272,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933662</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4194,6 +4374,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933756</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4291,6 +4476,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933933</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4388,6 +4578,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933992</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4485,6 +4680,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934071</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4582,6 +4782,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934129</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4679,6 +4884,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934386</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4776,6 +4986,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934557</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4873,6 +5088,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934709</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4970,6 +5190,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131927394</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5072,6 +5297,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928437</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5174,6 +5404,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930993</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5271,6 +5506,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928703</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5368,6 +5608,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934627</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5465,6 +5710,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926947</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5562,6 +5812,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934634</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5659,6 +5914,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968695</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5761,6 +6021,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928811</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5863,6 +6128,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931509</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5965,6 +6235,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932078</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6067,6 +6342,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934127</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6169,6 +6449,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934550</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6271,6 +6556,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131927769</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6373,6 +6663,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930537</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6475,6 +6770,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931571</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6577,6 +6877,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932719</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6679,6 +6984,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933577</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6781,6 +7091,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933749</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6883,6 +7198,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933987</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6985,6 +7305,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934170</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7087,6 +7412,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932655</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7189,6 +7519,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928063</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7291,6 +7626,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932657</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7396,6 +7736,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131970205</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7498,6 +7843,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933399</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7603,6 +7953,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131970210</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7700,6 +8055,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966587</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7797,6 +8157,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971353</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7898,6 +8263,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926672</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8004,6 +8374,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131929195</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8105,6 +8480,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131929915</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8211,6 +8591,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930182</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8317,6 +8702,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930390</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8423,6 +8813,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930457</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8524,6 +8919,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931220</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8625,6 +9025,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934382</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8726,6 +9131,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134957913</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8827,6 +9237,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961352</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8924,6 +9339,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933929</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9029,6 +9449,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67164036</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9126,6 +9551,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933651</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9223,6 +9653,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934622</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9320,6 +9755,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934704</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9417,8 +9857,103 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926950</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 9412-2026 artfynd.xlsx
+++ b/artfynd/A 9412-2026 artfynd.xlsx
@@ -1096,7 +1096,7 @@
         <v>134964386</v>
       </c>
       <c r="B6" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>134968695</v>
       </c>
       <c r="B52" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>134966587</v>
       </c>
       <c r="B72" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>134971353</v>
       </c>
       <c r="B73" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>134957913</v>
       </c>
       <c r="B82" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>134961352</v>
       </c>
       <c r="B83" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
